--- a/docs/Balance/SkillDamageBalance.xlsx
+++ b/docs/Balance/SkillDamageBalance.xlsx
@@ -2,18 +2,18 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R910f66c2750f4d45"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings" sheetId="2" r:id="R888beea101e7404e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Combatants" sheetId="3" r:id="R91394c12bc9643a1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BP Pipeline" sheetId="4" r:id="Rde56ebe3401a4469"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Race Profiles" sheetId="5" r:id="R8f800c68a4364f7e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Race Balance" sheetId="6" r:id="R61b624917059487d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Balance" sheetId="7" r:id="R3bfb8a8470f34219"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Modifiers" sheetId="8" r:id="R419605269e2e4dde"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skill Catalog" sheetId="9" r:id="R2ed39e6f30994711"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Damage Calculator" sheetId="10" r:id="Rbd42ef8360934876"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="11" r:id="Red2e49ccd6c34741"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="12" r:id="Re36f9e7933234f1b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R5ed5485ffd4a47bc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings" sheetId="2" r:id="Rd813a01918eb4b71"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Combatants" sheetId="3" r:id="Rc336edff5ec34dd6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BP Pipeline" sheetId="4" r:id="Rc78a3f4d154047aa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Race Profiles" sheetId="5" r:id="R88dfd437bd194c74"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Race Balance" sheetId="6" r:id="Rf4c83eb29d114fee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Balance" sheetId="7" r:id="Rf0e2547505ab4e5b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Modifiers" sheetId="8" r:id="R26ec0d7512f444af"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skill Catalog" sheetId="9" r:id="R8d3e83e1ae8a45b4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Damage Calculator" sheetId="10" r:id="R4094d9616f834d52"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="11" r:id="R5984660df7054c5d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="12" r:id="R7a513f2c5db44fd3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -394,10 +394,8 @@
           <x:t xml:space="preserve">Damage basis</x:t>
         </x:is>
       </x:c>
-      <x:c r="B5" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Factors are equal-stat percentages. Physical damage uses Strength/Endurance; Ki uses Force/Resistance; both use BP^0.5 and the bounded stat term (2*source/(source+guard))^0.85. Offense/Defense affect hit outcomes only.</x:t>
-        </x:is>
+      <x:c r="B5" s="5" t="str">
+        <x:v>Factors are equal-stat percentages. Physical damage uses Strength/Endurance; Ki uses Force/Resistance; both use a linear BP ratio and the bounded stat term (2*source/(source+guard))^0.85. Offense/Defense affect hit outcomes only.</x:v>
       </x:c>
       <x:c r="C5" s="5" t="inlineStr">
         <x:is>
@@ -1700,10 +1698,8 @@
         <x:f>K22</x:f>
         <x:v>52</x:v>
       </x:c>
-      <x:c r="N22" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Cumulative beam factor</x:t>
-        </x:is>
+      <x:c r="N22" s="5" t="str">
+        <x:v>Lock uncapped; explosive budget 52</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -1758,10 +1754,8 @@
         <x:f>K23</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="N23" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Cumulative beam factor</x:t>
-        </x:is>
+      <x:c r="N23" s="5" t="str">
+        <x:v>Lock uncapped; explosive budget 4</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -1816,10 +1810,8 @@
         <x:f>K24</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="N24" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Cumulative beam factor</x:t>
-        </x:is>
+      <x:c r="N24" s="5" t="str">
+        <x:v>Lock uncapped; explosive budget 3</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -1874,10 +1866,8 @@
         <x:f>K25</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="N25" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Cumulative beam factor</x:t>
-        </x:is>
+      <x:c r="N25" s="5" t="str">
+        <x:v>Lock uncapped; explosive budget 3</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -1932,10 +1922,8 @@
         <x:f>K26</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="N26" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Cumulative beam factor</x:t>
-        </x:is>
+      <x:c r="N26" s="5" t="str">
+        <x:v>Lock uncapped; explosive budget 5</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -1990,10 +1978,8 @@
         <x:f>K27</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="N27" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Cumulative beam factor</x:t>
-        </x:is>
+      <x:c r="N27" s="5" t="str">
+        <x:v>Lock uncapped; explosive budget 8</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -2048,10 +2034,8 @@
         <x:f>K28</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="N28" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Cumulative beam factor</x:t>
-        </x:is>
+      <x:c r="N28" s="5" t="str">
+        <x:v>Lock uncapped; explosive budget 5</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
@@ -2106,10 +2090,8 @@
         <x:f>K29</x:f>
         <x:v>12</x:v>
       </x:c>
-      <x:c r="N29" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Cumulative beam factor</x:t>
-        </x:is>
+      <x:c r="N29" s="5" t="str">
+        <x:v>Lock uncapped; explosive budget 12</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
@@ -2164,10 +2146,8 @@
         <x:f>K30</x:f>
         <x:v>7</x:v>
       </x:c>
-      <x:c r="N30" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Cumulative beam factor</x:t>
-        </x:is>
+      <x:c r="N30" s="5" t="str">
+        <x:v>Lock uncapped; explosive budget 7</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
@@ -2222,10 +2202,8 @@
         <x:f>K31</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="N31" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Cumulative beam factor</x:t>
-        </x:is>
+      <x:c r="N31" s="5" t="str">
+        <x:v>Lock uncapped; explosive budget 6</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
@@ -2330,6 +2308,58 @@
       </x:c>
       <x:c r="N33" t="str">
         <x:v>Strength-scaled direct plus splash</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" t="str">
+        <x:v>Echoing Slash</x:v>
+      </x:c>
+      <x:c r="B34" t="str">
+        <x:v>Physical</x:v>
+      </x:c>
+      <x:c r="C34" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D34" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F34" t="n">
+        <x:f>POWER(Combatants!$E$4/Combatants!$E$5,Settings!$B$6)</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G34" t="n">
+        <x:f>IF(B34="Physical",POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7),POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7))</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H34" t="n">
+        <x:f>1</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I34" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J34" t="n">
+        <x:f>C34*F34*G34*Combatants!$O$5</x:f>
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="K34" t="n">
+        <x:f>J34*D34</x:f>
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="L34" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M34" t="n">
+        <x:f>K34</x:f>
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="N34" t="str">
+        <x:v>Strength-scaled cutting wave</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2341,7 +2371,7 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="28" customWidth="1"/>
+    <x:col min="1" max="1" width="42" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="18" customWidth="1"/>
     <x:col min="3" max="3" width="18" customWidth="1"/>
     <x:col min="4" max="4" width="18" customWidth="1"/>
@@ -2630,6 +2660,44 @@
       </x:c>
       <x:c r="E13" t="str">
         <x:v>8 x2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" t="str">
+        <x:v>Echoing Slash</x:v>
+      </x:c>
+      <x:c r="B14" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C14" t="n">
+        <x:f>'Damage Calculator'!J34</x:f>
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D14" t="n">
+        <x:f>C14-B14</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E14" t="str">
+        <x:v>Strength-scaled factor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" t="str">
+        <x:v>Standard Beam at 13000 BP vs 200 BP</x:v>
+      </x:c>
+      <x:c r="B15" t="n">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="C15" t="n">
+        <x:f>3*POWER(13000/200,Settings!$B$6)</x:f>
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="D15" t="n">
+        <x:f>C15-B15</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E15" t="str">
+        <x:v>Linear BP scaling makes a 65x advantage immediately decisive</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3022,18 +3090,16 @@
           <x:t xml:space="preserve">BP exponent</x:t>
         </x:is>
       </x:c>
-      <x:c r="B6" s="3">
-        <x:v>0.5</x:v>
+      <x:c r="B6" s="3" t="n">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C6" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">ratio exponent</x:t>
         </x:is>
       </x:c>
-      <x:c r="D6" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">GlobalCombatSettings.dm:52</x:t>
-        </x:is>
+      <x:c r="D6" s="5" t="str">
+        <x:v>Combat/DamageScaling.dm</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -3381,6 +3447,20 @@
         <x:v>multiplier</x:v>
       </x:c>
       <x:c r="D24" t="str">
+        <x:v>GlobalCombatSettings.dm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" t="str">
+        <x:v>Beam clash input pulse</x:v>
+      </x:c>
+      <x:c r="B25" t="n">
+        <x:v>1.15</x:v>
+      </x:c>
+      <x:c r="C25" t="str">
+        <x:v>multiplier</x:v>
+      </x:c>
+      <x:c r="D25" t="str">
         <x:v>GlobalCombatSettings.dm</x:v>
       </x:c>
     </x:row>
@@ -11467,7 +11547,7 @@
         </x:is>
       </x:c>
       <x:c r="N27" s="5" t="str">
-        <x:v>Highest factor; 3s restart cooldown</x:v>
+        <x:v>Lock ticks uncapped; explosive budget 52; 3s restart cooldown</x:v>
       </x:c>
       <x:c r="O27" s="5" t="inlineStr">
         <x:is>
@@ -11530,7 +11610,7 @@
         </x:is>
       </x:c>
       <x:c r="N28" s="5" t="str">
-        <x:v>Cumulative budget 4; 3s restart cooldown</x:v>
+        <x:v>Lock ticks uncapped; explosive budget 4; 3s restart cooldown</x:v>
       </x:c>
       <x:c r="O28" s="5" t="inlineStr">
         <x:is>
@@ -11593,7 +11673,7 @@
         </x:is>
       </x:c>
       <x:c r="N29" s="5" t="str">
-        <x:v>Cumulative budget 3; 3s restart cooldown</x:v>
+        <x:v>Lock ticks uncapped; explosive budget 3; 3s restart cooldown</x:v>
       </x:c>
       <x:c r="O29" s="5" t="inlineStr">
         <x:is>
@@ -11656,7 +11736,7 @@
         </x:is>
       </x:c>
       <x:c r="N30" s="5" t="str">
-        <x:v>Cumulative budget 3; 3s restart cooldown</x:v>
+        <x:v>Lock ticks uncapped; explosive budget 3; 3s restart cooldown</x:v>
       </x:c>
       <x:c r="O30" s="5" t="inlineStr">
         <x:is>
@@ -11719,7 +11799,7 @@
         </x:is>
       </x:c>
       <x:c r="N31" s="5" t="str">
-        <x:v>Shield pierce; 3s restart cooldown</x:v>
+        <x:v>Lock ticks uncapped; explosive budget 5; shield pierce; 3s cooldown</x:v>
       </x:c>
       <x:c r="O31" s="5" t="inlineStr">
         <x:is>
@@ -11782,7 +11862,7 @@
         </x:is>
       </x:c>
       <x:c r="N32" s="5" t="str">
-        <x:v>Cumulative budget 8; 3s restart cooldown</x:v>
+        <x:v>Lock ticks uncapped; explosive budget 8; 3s restart cooldown</x:v>
       </x:c>
       <x:c r="O32" s="5" t="inlineStr">
         <x:is>
@@ -11845,7 +11925,7 @@
         </x:is>
       </x:c>
       <x:c r="N33" s="5" t="str">
-        <x:v>Range utility; 3s restart cooldown</x:v>
+        <x:v>Lock ticks uncapped; explosive budget 5; range utility; 3s cooldown</x:v>
       </x:c>
       <x:c r="O33" s="5" t="inlineStr">
         <x:is>
@@ -11908,7 +11988,7 @@
         </x:is>
       </x:c>
       <x:c r="N34" s="5" t="str">
-        <x:v>Cumulative budget 12; 3s restart cooldown</x:v>
+        <x:v>Lock ticks uncapped; explosive budget 12; 3s restart cooldown</x:v>
       </x:c>
       <x:c r="O34" s="5" t="inlineStr">
         <x:is>
@@ -11971,7 +12051,7 @@
         </x:is>
       </x:c>
       <x:c r="N35" s="5" t="str">
-        <x:v>Cumulative budget 7; 3s restart cooldown</x:v>
+        <x:v>Lock ticks uncapped; explosive budget 7; 3s restart cooldown</x:v>
       </x:c>
       <x:c r="O35" s="5" t="inlineStr">
         <x:is>
@@ -12034,7 +12114,7 @@
         </x:is>
       </x:c>
       <x:c r="N36" s="5" t="str">
-        <x:v>Range utility; 3s restart cooldown</x:v>
+        <x:v>Lock ticks uncapped; explosive budget 6; range utility; 3s cooldown</x:v>
       </x:c>
       <x:c r="O36" s="5" t="inlineStr">
         <x:is>
@@ -12789,6 +12869,53 @@
         <x:v>Strength-scaled direct plus splash; weapon required; budget cap 16</x:v>
       </x:c>
       <x:c r="O48" t="str">
+        <x:v>Combat/TenkaichiSpecialStyles.dm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49" t="str">
+        <x:v>Echoing Slash</x:v>
+      </x:c>
+      <x:c r="B49" t="str">
+        <x:v>/obj/Attacks/TenkaichiSpecialStyle/ChargedProjectile/EchoingSlash</x:v>
+      </x:c>
+      <x:c r="C49" t="str">
+        <x:v>Test package</x:v>
+      </x:c>
+      <x:c r="D49" t="str">
+        <x:v>Physical</x:v>
+      </x:c>
+      <x:c r="E49" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="F49" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I49" t="n">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="J49" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="K49" t="str">
+        <x:v>0.8s charge</x:v>
+      </x:c>
+      <x:c r="L49" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="M49" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="N49" t="str">
+        <x:v>Strength-scaled cutting wave; weapon required; no explosion</x:v>
+      </x:c>
+      <x:c r="O49" t="str">
         <x:v>Combat/TenkaichiSpecialStyles.dm</x:v>
       </x:c>
     </x:row>

--- a/docs/Balance/SkillDamageBalance.xlsx
+++ b/docs/Balance/SkillDamageBalance.xlsx
@@ -2,18 +2,18 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R5ed5485ffd4a47bc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings" sheetId="2" r:id="Rd813a01918eb4b71"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Combatants" sheetId="3" r:id="Rc336edff5ec34dd6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BP Pipeline" sheetId="4" r:id="Rc78a3f4d154047aa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Race Profiles" sheetId="5" r:id="R88dfd437bd194c74"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Race Balance" sheetId="6" r:id="Rf4c83eb29d114fee"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Balance" sheetId="7" r:id="Rf0e2547505ab4e5b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Modifiers" sheetId="8" r:id="R26ec0d7512f444af"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skill Catalog" sheetId="9" r:id="R8d3e83e1ae8a45b4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Damage Calculator" sheetId="10" r:id="R4094d9616f834d52"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="11" r:id="R5984660df7054c5d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="12" r:id="R7a513f2c5db44fd3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="Rf96eeaea2e8f4134"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings" sheetId="2" r:id="R0ecf107570d34b01"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Combatants" sheetId="3" r:id="R5917678925404a13"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BP Pipeline" sheetId="4" r:id="R7361f5b1df214dd6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Race Profiles" sheetId="5" r:id="Rf3e94afb944b45d7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Race Balance" sheetId="6" r:id="R7dd9a7bda64842cc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Balance" sheetId="7" r:id="R0e3033e12cca4bd7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Modifiers" sheetId="8" r:id="R0df48cfa05f442a9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skill Catalog" sheetId="9" r:id="R926dbc767f164fb8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Damage Calculator" sheetId="10" r:id="R378d01ee77794160"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="11" r:id="R647331bb03c340b0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="12" r:id="Rb06aa2d2a7f84aeb"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -460,10 +460,8 @@
           <x:t xml:space="preserve">Ki speed</x:t>
         </x:is>
       </x:c>
-      <x:c r="B9" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Non-beam Ki projectiles use a 0.5 decisecond cadence at 60 FPS. Beam and Spirit Bomb delays remain skill-specific.</x:t>
-        </x:is>
+      <x:c r="B9" s="5" t="str">
+        <x:v>Non-beam Ki projectiles use a 0.5 decisecond movement cadence at 60 FPS. Basic Blast fires a three-pellet fan on a 0.75-decisecond base refire with 30% damage and 20% Energy cost per pellet. Beam and Spirit Bomb delays remain skill-specific.</x:v>
       </x:c>
       <x:c r="C9" s="5" t="inlineStr">
         <x:is>
@@ -10731,56 +10729,38 @@
           <x:t xml:space="preserve">Ki</x:t>
         </x:is>
       </x:c>
-      <x:c r="E15" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">0.35-0.5</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F15" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1-4</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G15">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H15" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Optional equal splash</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I15" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Dynamic</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J15" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Dynamic</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K15" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">No charge</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="L15">
+      <x:c r="E15" t="str">
+        <x:v>0.105-0.15</x:v>
+      </x:c>
+      <x:c r="F15" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H15" t="str">
+        <x:v>Lead only</x:v>
+      </x:c>
+      <x:c r="I15" t="str">
+        <x:v>20% per pellet</x:v>
+      </x:c>
+      <x:c r="J15" t="str">
+        <x:v>Dynamic</x:v>
+      </x:c>
+      <x:c r="K15" s="5" t="str">
+        <x:v>0.75ds base refire</x:v>
+      </x:c>
+      <x:c r="L15" t="n">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="M15" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">None</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="N15" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Shared factor budget 4</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O15" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ProjectileSystem/Blasts.dm; SkillEngine.dm</x:t>
-        </x:is>
+      <x:c r="M15" s="5" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="N15" s="5" t="str">
+        <x:v>3-pellet fan; shared budget 0.6; lead utility; caps 24/owner and 256/global</x:v>
+      </x:c>
+      <x:c r="O15" s="5" t="str">
+        <x:v>ProjectileSystem/Blasts.dm; SkillEngine.dm</x:v>
       </x:c>
     </x:row>
     <x:row r="16">

--- a/docs/Balance/SkillDamageBalance.xlsx
+++ b/docs/Balance/SkillDamageBalance.xlsx
@@ -2,18 +2,18 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="Rf96eeaea2e8f4134"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings" sheetId="2" r:id="R0ecf107570d34b01"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Combatants" sheetId="3" r:id="R5917678925404a13"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BP Pipeline" sheetId="4" r:id="R7361f5b1df214dd6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Race Profiles" sheetId="5" r:id="Rf3e94afb944b45d7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Race Balance" sheetId="6" r:id="R7dd9a7bda64842cc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Balance" sheetId="7" r:id="R0e3033e12cca4bd7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Modifiers" sheetId="8" r:id="R0df48cfa05f442a9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skill Catalog" sheetId="9" r:id="R926dbc767f164fb8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Damage Calculator" sheetId="10" r:id="R378d01ee77794160"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="11" r:id="R647331bb03c340b0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="12" r:id="Rb06aa2d2a7f84aeb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R4e5000d0306043a8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings" sheetId="2" r:id="Rcaf2220e73c5405f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Combatants" sheetId="3" r:id="R238457ab2c1f4241"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BP Pipeline" sheetId="4" r:id="R8dd6a34a3b064324"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Race Profiles" sheetId="5" r:id="R9d59740f4b9d49b2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Race Balance" sheetId="6" r:id="Rb1362c7a67db4e82"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Balance" sheetId="7" r:id="Rb0bad63b9a154cfa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Modifiers" sheetId="8" r:id="R8c9f497cd0184244"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skill Catalog" sheetId="9" r:id="Ra6dd12ca988043aa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Damage Calculator" sheetId="10" r:id="Rd7872e068d3d4b15"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="11" r:id="Rc8f143606e0a4d91"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="12" r:id="Rd2044f5815714499"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -729,10 +729,10 @@
           <x:t xml:space="preserve">Physical</x:t>
         </x:is>
       </x:c>
-      <x:c r="C6" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D6" s="3">
+      <x:c r="C6" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D6" s="3" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="E6" s="3">
@@ -756,11 +756,11 @@
       </x:c>
       <x:c r="J6" s="4" t="n">
         <x:f>C6*F6*G6*Combatants!$O$5</x:f>
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="K6" s="4" t="n">
         <x:f>J6*D6</x:f>
-        <x:v>5</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="L6" s="4" t="n">
         <x:f>0</x:f>
@@ -768,12 +768,10 @@
       </x:c>
       <x:c r="M6" s="4" t="n">
         <x:f>K6</x:f>
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="N6" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">5-hit maximum</x:t>
-        </x:is>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="N6" s="5" t="str">
+        <x:v>5-hit maximum; finisher knockback</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -787,10 +785,10 @@
           <x:t xml:space="preserve">Physical</x:t>
         </x:is>
       </x:c>
-      <x:c r="C7" s="3">
-        <x:v>0.25</x:v>
-      </x:c>
-      <x:c r="D7" s="3">
+      <x:c r="C7" s="3" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="D7" s="3" t="n">
         <x:v>24</x:v>
       </x:c>
       <x:c r="E7" s="3">
@@ -814,11 +812,11 @@
       </x:c>
       <x:c r="J7" s="4" t="n">
         <x:f>C7*F7*G7*Combatants!$O$5</x:f>
-        <x:v>0.25</x:v>
+        <x:v>0.5</x:v>
       </x:c>
       <x:c r="K7" s="4" t="n">
         <x:f>J7*D7</x:f>
-        <x:v>6</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="L7" s="4" t="n">
         <x:f>0</x:f>
@@ -826,7 +824,7 @@
       </x:c>
       <x:c r="M7" s="4" t="n">
         <x:f>K7</x:f>
-        <x:v>6</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="N7" s="5" t="inlineStr">
         <x:is>
@@ -1249,10 +1247,10 @@
           <x:t xml:space="preserve">Ki</x:t>
         </x:is>
       </x:c>
-      <x:c r="C15" s="3">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D15" s="3">
+      <x:c r="C15" s="3" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D15" s="3" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="E15" s="3">
@@ -1276,11 +1274,11 @@
       </x:c>
       <x:c r="J15" s="4" t="n">
         <x:f>C15*F15*G15*Combatants!$O$5</x:f>
-        <x:v>6</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="K15" s="4" t="n">
         <x:f>J15*D15</x:f>
-        <x:v>6</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="L15" s="4" t="n">
         <x:f>0</x:f>
@@ -1288,12 +1286,10 @@
       </x:c>
       <x:c r="M15" s="4" t="n">
         <x:f>K15</x:f>
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="N15" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Owner-immune</x:t>
-        </x:is>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="N15" s="5" t="str">
+        <x:v>Owner-immune; 50% decay after each landed pierce</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -1307,10 +1303,10 @@
           <x:t xml:space="preserve">Ki</x:t>
         </x:is>
       </x:c>
-      <x:c r="C16" s="3">
-        <x:v>3.5</x:v>
-      </x:c>
-      <x:c r="D16" s="3">
+      <x:c r="C16" s="3" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D16" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="E16" s="3">
@@ -1334,11 +1330,11 @@
       </x:c>
       <x:c r="J16" s="4" t="n">
         <x:f>C16*F16*G16*Combatants!$O$5</x:f>
-        <x:v>3.5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="K16" s="4" t="n">
         <x:f>J16*D16</x:f>
-        <x:v>7</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="L16" s="4" t="n">
         <x:f>0</x:f>
@@ -1346,12 +1342,10 @@
       </x:c>
       <x:c r="M16" s="4" t="n">
         <x:f>K16</x:f>
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="N16" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Direct plus splash; owner-immune</x:t>
-        </x:is>
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="N16" s="5" t="str">
+        <x:v>Direct plus splash; owner-immune</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -1423,11 +1417,11 @@
           <x:t xml:space="preserve">Ki</x:t>
         </x:is>
       </x:c>
-      <x:c r="C18" s="3">
-        <x:v>0.4</x:v>
-      </x:c>
-      <x:c r="D18" s="3">
-        <x:v>20</x:v>
+      <x:c r="C18" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D18" s="3" t="n">
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E18" s="3">
         <x:v>0</x:v>
@@ -1450,11 +1444,11 @@
       </x:c>
       <x:c r="J18" s="4" t="n">
         <x:f>C18*F18*G18*Combatants!$O$5</x:f>
-        <x:v>0.4</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K18" s="4" t="n">
         <x:f>J18*D18</x:f>
-        <x:v>8</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="L18" s="4" t="n">
         <x:f>0</x:f>
@@ -1462,12 +1456,10 @@
       </x:c>
       <x:c r="M18" s="4" t="n">
         <x:f>K18</x:f>
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="N18" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Emission cap</x:t>
-        </x:is>
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="N18" s="5" t="str">
+        <x:v>20 emissions; shared budget caps actual total at 16</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -2467,12 +2459,12 @@
           <x:t xml:space="preserve">Wolf Fang per hit</x:t>
         </x:is>
       </x:c>
-      <x:c r="B5">
-        <x:v>1</x:v>
+      <x:c r="B5" t="n">
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C5" s="4" t="n">
         <x:f>'Damage Calculator'!J6</x:f>
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D5" s="4" t="n">
         <x:f>C5-B5</x:f>
@@ -2490,12 +2482,12 @@
           <x:t xml:space="preserve">Wolf Fang five hits</x:t>
         </x:is>
       </x:c>
-      <x:c r="B6">
-        <x:v>5</x:v>
+      <x:c r="B6" t="n">
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C6" s="4" t="n">
         <x:f>'Damage Calculator'!J6*5</x:f>
-        <x:v>5</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D6" s="4" t="n">
         <x:f>C6-B6</x:f>
@@ -2513,12 +2505,12 @@
           <x:t xml:space="preserve">Hundred Crack per hit</x:t>
         </x:is>
       </x:c>
-      <x:c r="B7">
-        <x:v>0.25</x:v>
+      <x:c r="B7" t="n">
+        <x:v>0.5</x:v>
       </x:c>
       <x:c r="C7" s="4" t="n">
         <x:f>'Damage Calculator'!J7</x:f>
-        <x:v>0.25</x:v>
+        <x:v>0.5</x:v>
       </x:c>
       <x:c r="D7" s="4" t="n">
         <x:f>C7-B7</x:f>
@@ -2536,12 +2528,12 @@
           <x:t xml:space="preserve">Hundred Crack minimum total</x:t>
         </x:is>
       </x:c>
-      <x:c r="B8">
-        <x:v>6</x:v>
+      <x:c r="B8" t="n">
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C8" s="4" t="n">
         <x:f>'Damage Calculator'!J7*24</x:f>
-        <x:v>6</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D8" s="4" t="n">
         <x:f>C8-B8</x:f>
@@ -10095,8 +10087,8 @@
           <x:t xml:space="preserve">Physical</x:t>
         </x:is>
       </x:c>
-      <x:c r="E5">
-        <x:v>1</x:v>
+      <x:c r="E5" t="n">
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F5">
         <x:v>5</x:v>
@@ -10128,10 +10120,8 @@
           <x:t xml:space="preserve">None</x:t>
         </x:is>
       </x:c>
-      <x:c r="N5" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Five-hit budget 5</x:t>
-        </x:is>
+      <x:c r="N5" s="5" t="str">
+        <x:v>Five-hit budget 10; +15 accuracy; knockback only on the finisher</x:v>
       </x:c>
       <x:c r="O5" s="5" t="inlineStr">
         <x:is>
@@ -10160,8 +10150,8 @@
           <x:t xml:space="preserve">Physical</x:t>
         </x:is>
       </x:c>
-      <x:c r="E6">
-        <x:v>0.25</x:v>
+      <x:c r="E6" t="n">
+        <x:v>0.5</x:v>
       </x:c>
       <x:c r="F6">
         <x:v>24</x:v>
@@ -10193,10 +10183,8 @@
           <x:t xml:space="preserve">None</x:t>
         </x:is>
       </x:c>
-      <x:c r="N6" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Exactly 24 attempts; budget 6</x:t>
-        </x:is>
+      <x:c r="N6" s="5" t="str">
+        <x:v>Exactly 24 attempts; budget 12</x:v>
       </x:c>
       <x:c r="O6" s="5" t="inlineStr">
         <x:is>
@@ -10225,10 +10213,8 @@
           <x:t xml:space="preserve">Physical</x:t>
         </x:is>
       </x:c>
-      <x:c r="E7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2-8</x:t>
-        </x:is>
+      <x:c r="E7" t="str">
+        <x:v>3-12</x:v>
       </x:c>
       <x:c r="F7">
         <x:v>1</x:v>
@@ -10260,10 +10246,8 @@
           <x:t xml:space="preserve">None</x:t>
         </x:is>
       </x:c>
-      <x:c r="N7" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Factor scales 0.25 per completed step; no second BP ratio</x:t>
-        </x:is>
+      <x:c r="N7" s="5" t="str">
+        <x:v>Factor scales 0.4 per completed step; no second BP ratio</x:v>
       </x:c>
       <x:c r="O7" s="5" t="inlineStr">
         <x:is>
@@ -10292,8 +10276,8 @@
           <x:t xml:space="preserve">Physical</x:t>
         </x:is>
       </x:c>
-      <x:c r="E8">
-        <x:v>8</x:v>
+      <x:c r="E8" t="n">
+        <x:v>12</x:v>
       </x:c>
       <x:c r="F8">
         <x:v>2</x:v>
@@ -10325,10 +10309,8 @@
           <x:t xml:space="preserve">None</x:t>
         </x:is>
       </x:c>
-      <x:c r="N8" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Two hits: 5 and 3</x:t>
-        </x:is>
+      <x:c r="N8" s="5" t="str">
+        <x:v>Two hits: 7 and 5</x:v>
       </x:c>
       <x:c r="O8" s="5" t="inlineStr">
         <x:is>
@@ -10357,8 +10339,8 @@
           <x:t xml:space="preserve">Physical</x:t>
         </x:is>
       </x:c>
-      <x:c r="E9">
-        <x:v>6</x:v>
+      <x:c r="E9" t="n">
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F9">
         <x:v>1</x:v>
@@ -10372,13 +10354,11 @@
       <x:c r="I9">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J9">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="K9" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2s</x:t>
-        </x:is>
+      <x:c r="J9" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="K9" s="5" t="str">
+        <x:v>1s charge</x:v>
       </x:c>
       <x:c r="L9">
         <x:v>3</x:v>
@@ -10420,8 +10400,8 @@
           <x:t xml:space="preserve">Physical</x:t>
         </x:is>
       </x:c>
-      <x:c r="E10">
-        <x:v>4</x:v>
+      <x:c r="E10" t="n">
+        <x:v>7.5</x:v>
       </x:c>
       <x:c r="F10">
         <x:v>1</x:v>
@@ -10438,10 +10418,8 @@
       <x:c r="J10">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="K10" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1s</x:t>
-        </x:is>
+      <x:c r="K10" s="5" t="str">
+        <x:v>1s charge</x:v>
       </x:c>
       <x:c r="L10">
         <x:v>3</x:v>
@@ -10979,8 +10957,8 @@
           <x:t xml:space="preserve">Ki</x:t>
         </x:is>
       </x:c>
-      <x:c r="E19">
-        <x:v>6</x:v>
+      <x:c r="E19" t="n">
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F19">
         <x:v>1</x:v>
@@ -11010,10 +10988,8 @@
           <x:t xml:space="preserve">None</x:t>
         </x:is>
       </x:c>
-      <x:c r="N19" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Piercing, guided and owner-immune</x:t>
-        </x:is>
+      <x:c r="N19" s="5" t="str">
+        <x:v>Piercing, guided and owner-immune; 50% decay after each landed pierce</x:v>
       </x:c>
       <x:c r="O19" s="5" t="inlineStr">
         <x:is>
@@ -11042,8 +11018,8 @@
           <x:t xml:space="preserve">Ki</x:t>
         </x:is>
       </x:c>
-      <x:c r="E20">
-        <x:v>3.5</x:v>
+      <x:c r="E20" t="n">
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F20">
         <x:v>2</x:v>
@@ -11051,10 +11027,8 @@
       <x:c r="G20">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H20" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">3.5 splash</x:t>
-        </x:is>
+      <x:c r="H20" t="str">
+        <x:v>6 splash</x:v>
       </x:c>
       <x:c r="I20">
         <x:v>20</x:v>
@@ -11075,10 +11049,8 @@
           <x:t xml:space="preserve">None</x:t>
         </x:is>
       </x:c>
-      <x:c r="N20" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Guided, owner-immune; budget 7</x:t>
-        </x:is>
+      <x:c r="N20" s="5" t="str">
+        <x:v>Guided, owner-immune; budget 12</x:v>
       </x:c>
       <x:c r="O20" s="5" t="inlineStr">
         <x:is>
@@ -11172,8 +11144,8 @@
           <x:t xml:space="preserve">Ki</x:t>
         </x:is>
       </x:c>
-      <x:c r="E22">
-        <x:v>0.4</x:v>
+      <x:c r="E22" t="n">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F22">
         <x:v>20</x:v>
@@ -11203,10 +11175,8 @@
           <x:t xml:space="preserve">None</x:t>
         </x:is>
       </x:c>
-      <x:c r="N22" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Nondeflectable barrage capped at 20</x:t>
-        </x:is>
+      <x:c r="N22" s="5" t="str">
+        <x:v>Nondeflectable barrage; shared budget 16 per target</x:v>
       </x:c>
       <x:c r="O22" s="5" t="inlineStr">
         <x:is>

--- a/docs/Balance/SkillDamageBalance.xlsx
+++ b/docs/Balance/SkillDamageBalance.xlsx
@@ -2,18 +2,18 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R4e5000d0306043a8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings" sheetId="2" r:id="Rcaf2220e73c5405f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Combatants" sheetId="3" r:id="R238457ab2c1f4241"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BP Pipeline" sheetId="4" r:id="R8dd6a34a3b064324"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Race Profiles" sheetId="5" r:id="R9d59740f4b9d49b2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Race Balance" sheetId="6" r:id="Rb1362c7a67db4e82"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Balance" sheetId="7" r:id="Rb0bad63b9a154cfa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Modifiers" sheetId="8" r:id="R8c9f497cd0184244"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skill Catalog" sheetId="9" r:id="Ra6dd12ca988043aa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Damage Calculator" sheetId="10" r:id="Rd7872e068d3d4b15"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="11" r:id="Rc8f143606e0a4d91"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="12" r:id="Rd2044f5815714499"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="Rdc472dd354cf4e6f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings" sheetId="2" r:id="Rd325cce8717844bd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Combatants" sheetId="3" r:id="Rea424707be8945e7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BP Pipeline" sheetId="4" r:id="Rcd8d8e2fd0e44ab7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Race Profiles" sheetId="5" r:id="Reb63b0a8a13b4073"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Race Balance" sheetId="6" r:id="R5a8ec851c3c44a64"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Balance" sheetId="7" r:id="Rd209def21b2140fc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Modifiers" sheetId="8" r:id="Rf1fd77862aef4fec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skill Catalog" sheetId="9" r:id="Rb9a3de65aafe48ee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Damage Calculator" sheetId="10" r:id="R7b6cd4b9a25c4e22"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="11" r:id="Ra394f4e256f542aa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="12" r:id="Rfe692a93df8c469f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -394,8 +394,10 @@
           <x:t xml:space="preserve">Damage basis</x:t>
         </x:is>
       </x:c>
-      <x:c r="B5" s="5" t="str">
-        <x:v>Factors are equal-stat percentages. Physical damage uses Strength/Endurance; Ki uses Force/Resistance; both use a linear BP ratio and the bounded stat term (2*source/(source+guard))^0.85. Offense/Defense affect hit outcomes only.</x:v>
+      <x:c r="B5" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Factors are equal-stat percentages. Physical damage uses Strength/Endurance; Ki uses Force/Resistance; both use a linear BP ratio and the bounded stat term (2*source/(source+guard))^0.85. Offense/Defense affect hit outcomes only.</x:t>
+        </x:is>
       </x:c>
       <x:c r="C5" s="5" t="inlineStr">
         <x:is>
@@ -406,81 +408,100 @@
     <x:row r="6">
       <x:c r="A6" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">BP pipeline</x:t>
+          <x:t xml:space="preserve">Skill policy</x:t>
         </x:is>
       </x:c>
       <x:c r="B6" s="5" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">The BP Pipeline sheet exposes the major ordering stages. The game has additional situational branches; use current Effective BP in Combatants when exact runtime BP is known.</x:t>
+          <x:t xml:space="preserve">The 2.5-factor manual attack is the baseline. Standard invested skills target about five to seven basic hits, high-commitment attacks target eight to twelve, and self-risk finishers target sixteen or more. Cheap repeatable basics remain below these floors.</x:t>
         </x:is>
       </x:c>
       <x:c r="C6" s="5" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">BackgroundCode/StatLoop.dm:95-242</x:t>
+          <x:t xml:space="preserve">GlobalCombatSettings.dm; Skill Catalog</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Powerup and anger</x:t>
+          <x:t xml:space="preserve">BP pipeline</x:t>
         </x:is>
       </x:c>
       <x:c r="B7" s="5" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Current mixture is additive: anger/100 + BPpcnt/100 - 1 + Super Kaioken addition. It is not anger multiplied by powerup.</x:t>
+          <x:t xml:space="preserve">The BP Pipeline sheet exposes the major ordering stages. The game has additional situational branches; use current Effective BP in Combatants when exact runtime BP is known.</x:t>
         </x:is>
       </x:c>
       <x:c r="C7" s="5" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">BackgroundCode/StatLoop.dm:25-49</x:t>
+          <x:t xml:space="preserve">BackgroundCode/StatLoop.dm:95-242</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Cyber BP</x:t>
+          <x:t xml:space="preserve">Powerup and anger</x:t>
         </x:is>
       </x:c>
       <x:c r="B8" s="5" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">With current cyber_bp_cuts_natural_bp_by=0, any cyber BP replaces natural BP before cyber contribution is added. Overdrive multiplies cyber contribution by 1.5.</x:t>
+          <x:t xml:space="preserve">Current mixture is additive: anger/100 + BPpcnt/100 - 1 + Super Kaioken addition. It is not anger multiplied by powerup.</x:t>
         </x:is>
       </x:c>
       <x:c r="C8" s="5" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">BackgroundCode/StatLoop.dm:183-193</x:t>
+          <x:t xml:space="preserve">BackgroundCode/StatLoop.dm:25-49</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Ki speed</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B9" s="5" t="str">
-        <x:v>Non-beam Ki projectiles use a 0.5 decisecond movement cadence at 60 FPS. Basic Blast fires a three-pellet fan on a 0.75-decisecond base refire with 30% damage and 20% Energy cost per pellet. Beam and Spirit Bomb delays remain skill-specific.</x:v>
+          <x:t xml:space="preserve">Cyber BP</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B9" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">With current cyber_bp_cuts_natural_bp_by=0, any cyber BP replaces natural BP before cyber contribution is added. Overdrive multiplies cyber contribution by 1.5.</x:t>
+        </x:is>
       </x:c>
       <x:c r="C9" s="5" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">ProjectileSystem/Blasts.dm; SkillControllers.dm</x:t>
+          <x:t xml:space="preserve">BackgroundCode/StatLoop.dm:183-193</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="6" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">Ki speed</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B10" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Non-beam Ki projectiles use a 0.5 decisecond movement cadence at 60 FPS. Basic Blast fires a three-pellet fan on a 0.75-decisecond base refire with 30% damage and 20% Energy cost per pellet. Beam and Spirit Bomb delays remain skill-specific.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C10" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ProjectileSystem/Blasts.dm; SkillControllers.dm</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="6" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">Usage</x:t>
         </x:is>
       </x:c>
-      <x:c r="B10" s="5" t="inlineStr">
+      <x:c r="B11" s="5" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1. Set Combatants inputs. 2. Adjust BP Pipeline and copy its result if needed. 3. Review standardized skills in Damage Calculator. 4. Use Skill Catalog for custom formulas and timing.</x:t>
         </x:is>
       </x:c>
-      <x:c r="C10" s="5" t="inlineStr">
+      <x:c r="C11" s="5" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">This workbook</x:t>
         </x:is>
@@ -627,7 +648,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G4" s="4" t="n">
-        <x:f>IF(B4="Physical",POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7),POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7))</x:f>
+        <x:f>IF(B4="Physical",POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7),IF(B4="Hybrid",(POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7)+POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7))/2,POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="H4" s="4" t="n">
@@ -672,7 +693,7 @@
         </x:is>
       </x:c>
       <x:c r="C5" s="3">
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D5" s="3">
         <x:v>1</x:v>
@@ -685,7 +706,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G5" s="4" t="n">
-        <x:f>IF(B5="Physical",POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7),POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7))</x:f>
+        <x:f>IF(B5="Physical",POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7),IF(B5="Hybrid",(POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7)+POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7))/2,POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="H5" s="4" t="n">
@@ -698,11 +719,11 @@
       </x:c>
       <x:c r="J5" s="4" t="n">
         <x:f>C5*F5*G5*Combatants!$O$5</x:f>
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="K5" s="4" t="n">
         <x:f>J5*D5</x:f>
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="L5" s="4" t="n">
         <x:f>0</x:f>
@@ -710,7 +731,7 @@
       </x:c>
       <x:c r="M5" s="4" t="n">
         <x:f>K5</x:f>
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="N5" s="5" t="inlineStr">
         <x:is>
@@ -729,10 +750,10 @@
           <x:t xml:space="preserve">Physical</x:t>
         </x:is>
       </x:c>
-      <x:c r="C6" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D6" s="3" t="n">
+      <x:c r="C6" s="3">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D6" s="3">
         <x:v>5</x:v>
       </x:c>
       <x:c r="E6" s="3">
@@ -743,7 +764,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G6" s="4" t="n">
-        <x:f>IF(B6="Physical",POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7),POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7))</x:f>
+        <x:f>IF(B6="Physical",POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7),IF(B6="Hybrid",(POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7)+POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7))/2,POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="H6" s="4" t="n">
@@ -756,11 +777,11 @@
       </x:c>
       <x:c r="J6" s="4" t="n">
         <x:f>C6*F6*G6*Combatants!$O$5</x:f>
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="K6" s="4" t="n">
         <x:f>J6*D6</x:f>
-        <x:v>10</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="L6" s="4" t="n">
         <x:f>0</x:f>
@@ -768,10 +789,12 @@
       </x:c>
       <x:c r="M6" s="4" t="n">
         <x:f>K6</x:f>
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="N6" s="5" t="str">
-        <x:v>5-hit maximum; finisher knockback</x:v>
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="N6" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">5-hit maximum; finisher knockback</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -785,10 +808,10 @@
           <x:t xml:space="preserve">Physical</x:t>
         </x:is>
       </x:c>
-      <x:c r="C7" s="3" t="n">
-        <x:v>0.5</x:v>
-      </x:c>
-      <x:c r="D7" s="3" t="n">
+      <x:c r="C7" s="3">
+        <x:v>0.75</x:v>
+      </x:c>
+      <x:c r="D7" s="3">
         <x:v>24</x:v>
       </x:c>
       <x:c r="E7" s="3">
@@ -799,7 +822,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G7" s="4" t="n">
-        <x:f>IF(B7="Physical",POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7),POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7))</x:f>
+        <x:f>IF(B7="Physical",POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7),IF(B7="Hybrid",(POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7)+POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7))/2,POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="H7" s="4" t="n">
@@ -812,11 +835,11 @@
       </x:c>
       <x:c r="J7" s="4" t="n">
         <x:f>C7*F7*G7*Combatants!$O$5</x:f>
-        <x:v>0.5</x:v>
+        <x:v>0.75</x:v>
       </x:c>
       <x:c r="K7" s="4" t="n">
         <x:f>J7*D7</x:f>
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="L7" s="4" t="n">
         <x:f>0</x:f>
@@ -824,7 +847,7 @@
       </x:c>
       <x:c r="M7" s="4" t="n">
         <x:f>K7</x:f>
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="N7" s="5" t="inlineStr">
         <x:is>
@@ -843,8 +866,8 @@
           <x:t xml:space="preserve">Physical</x:t>
         </x:is>
       </x:c>
-      <x:c r="C8" s="3" t="n">
-        <x:v>3.5</x:v>
+      <x:c r="C8" s="3">
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D8" s="3">
         <x:v>1</x:v>
@@ -857,7 +880,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G8" s="4" t="n">
-        <x:f>IF(B8="Physical",POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7),POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7))</x:f>
+        <x:f>IF(B8="Physical",POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7),IF(B8="Hybrid",(POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7)+POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7))/2,POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="H8" s="4" t="n">
@@ -870,11 +893,11 @@
       </x:c>
       <x:c r="J8" s="4" t="n">
         <x:f>C8*F8*G8*Combatants!$O$5</x:f>
-        <x:v>3.5</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="K8" s="4" t="n">
         <x:f>J8*D8</x:f>
-        <x:v>3.5</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="L8" s="4" t="n">
         <x:f>0</x:f>
@@ -882,7 +905,7 @@
       </x:c>
       <x:c r="M8" s="4" t="n">
         <x:f>K8</x:f>
-        <x:v>3.5</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="N8" s="5" t="inlineStr">
         <x:is>
@@ -902,7 +925,7 @@
         </x:is>
       </x:c>
       <x:c r="C9" s="3">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D9" s="3">
         <x:v>1</x:v>
@@ -915,7 +938,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G9" s="4" t="n">
-        <x:f>IF(B9="Physical",POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7),POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7))</x:f>
+        <x:f>IF(B9="Physical",POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7),IF(B9="Hybrid",(POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7)+POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7))/2,POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="H9" s="4" t="n">
@@ -928,11 +951,11 @@
       </x:c>
       <x:c r="J9" s="4" t="n">
         <x:f>C9*F9*G9*Combatants!$O$5</x:f>
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="K9" s="4" t="n">
         <x:f>J9*D9</x:f>
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="L9" s="4" t="n">
         <x:f>0</x:f>
@@ -940,7 +963,7 @@
       </x:c>
       <x:c r="M9" s="4" t="n">
         <x:f>K9</x:f>
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="N9" s="5" t="inlineStr">
         <x:is>
@@ -959,10 +982,10 @@
           <x:t xml:space="preserve">Physical</x:t>
         </x:is>
       </x:c>
-      <x:c r="C10" s="3" t="n">
-        <x:v>0.55</x:v>
-      </x:c>
-      <x:c r="D10" s="3" t="n">
+      <x:c r="C10" s="3">
+        <x:v>0.8</x:v>
+      </x:c>
+      <x:c r="D10" s="3">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E10" s="3">
@@ -973,7 +996,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G10" s="4" t="n">
-        <x:f>IF(B10="Physical",POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7),POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7))</x:f>
+        <x:f>IF(B10="Physical",POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7),IF(B10="Hybrid",(POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7)+POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7))/2,POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="H10" s="4" t="n">
@@ -986,11 +1009,11 @@
       </x:c>
       <x:c r="J10" s="4" t="n">
         <x:f>C10*F10*G10*Combatants!$O$5</x:f>
-        <x:v>0.55</x:v>
+        <x:v>0.8</x:v>
       </x:c>
       <x:c r="K10" s="4" t="n">
         <x:f>J10*D10</x:f>
-        <x:v>8.25</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="L10" s="4" t="n">
         <x:f>0</x:f>
@@ -998,10 +1021,12 @@
       </x:c>
       <x:c r="M10" s="4" t="n">
         <x:f>K10</x:f>
-        <x:v>8.25</x:v>
-      </x:c>
-      <x:c r="N10" s="5" t="str">
-        <x:v>Maximum 15 hits</x:v>
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="N10" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Maximum 15 hits</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -1015,8 +1040,8 @@
           <x:t xml:space="preserve">Physical</x:t>
         </x:is>
       </x:c>
-      <x:c r="C11" s="3" t="n">
-        <x:v>8</x:v>
+      <x:c r="C11" s="3">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D11" s="3">
         <x:v>1</x:v>
@@ -1029,7 +1054,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G11" s="4" t="n">
-        <x:f>IF(B11="Physical",POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7),POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7))</x:f>
+        <x:f>IF(B11="Physical",POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7),IF(B11="Hybrid",(POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7)+POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7))/2,POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="H11" s="4" t="n">
@@ -1042,11 +1067,11 @@
       </x:c>
       <x:c r="J11" s="4" t="n">
         <x:f>C11*F11*G11*Combatants!$O$5</x:f>
-        <x:v>8</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K11" s="4" t="n">
         <x:f>J11*D11</x:f>
-        <x:v>8</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="L11" s="4" t="n">
         <x:f>0</x:f>
@@ -1054,7 +1079,7 @@
       </x:c>
       <x:c r="M11" s="4" t="n">
         <x:f>K11</x:f>
-        <x:v>8</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="N11" s="5" t="inlineStr">
         <x:is>
@@ -1074,7 +1099,7 @@
         </x:is>
       </x:c>
       <x:c r="C12" s="3">
-        <x:v>22</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D12" s="3">
         <x:v>2</x:v>
@@ -1087,7 +1112,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G12" s="4" t="n">
-        <x:f>IF(B12="Physical",POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7),POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7))</x:f>
+        <x:f>IF(B12="Physical",POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7),IF(B12="Hybrid",(POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7)+POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7))/2,POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="H12" s="4" t="n">
@@ -1100,11 +1125,11 @@
       </x:c>
       <x:c r="J12" s="4" t="n">
         <x:f>C12*F12*G12*Combatants!$O$5</x:f>
-        <x:v>22</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K12" s="4" t="n">
         <x:f>J12*D12</x:f>
-        <x:v>44</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="L12" s="4" t="n">
         <x:f>0</x:f>
@@ -1112,7 +1137,7 @@
       </x:c>
       <x:c r="M12" s="4" t="n">
         <x:f>K12</x:f>
-        <x:v>44</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="N12" s="5" t="inlineStr">
         <x:is>
@@ -1132,7 +1157,7 @@
         </x:is>
       </x:c>
       <x:c r="C13" s="3">
-        <x:v>4</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D13" s="3">
         <x:v>2</x:v>
@@ -1145,7 +1170,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G13" s="4" t="n">
-        <x:f>IF(B13="Physical",POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7),POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7))</x:f>
+        <x:f>IF(B13="Physical",POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7),IF(B13="Hybrid",(POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7)+POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7))/2,POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="H13" s="4" t="n">
@@ -1158,11 +1183,11 @@
       </x:c>
       <x:c r="J13" s="4" t="n">
         <x:f>C13*F13*G13*Combatants!$O$5</x:f>
-        <x:v>4</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="K13" s="4" t="n">
         <x:f>J13*D13</x:f>
-        <x:v>8</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="L13" s="4" t="n">
         <x:f>0</x:f>
@@ -1170,7 +1195,7 @@
       </x:c>
       <x:c r="M13" s="4" t="n">
         <x:f>K13</x:f>
-        <x:v>8</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="N13" s="5" t="inlineStr">
         <x:is>
@@ -1190,7 +1215,7 @@
         </x:is>
       </x:c>
       <x:c r="C14" s="3">
-        <x:v>2.5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D14" s="3">
         <x:v>2</x:v>
@@ -1203,7 +1228,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G14" s="4" t="n">
-        <x:f>IF(B14="Physical",POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7),POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7))</x:f>
+        <x:f>IF(B14="Physical",POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7),IF(B14="Hybrid",(POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7)+POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7))/2,POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="H14" s="4" t="n">
@@ -1216,11 +1241,11 @@
       </x:c>
       <x:c r="J14" s="4" t="n">
         <x:f>C14*F14*G14*Combatants!$O$5</x:f>
-        <x:v>2.5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="K14" s="4" t="n">
         <x:f>J14*D14</x:f>
-        <x:v>5</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="L14" s="4" t="n">
         <x:f>0</x:f>
@@ -1228,7 +1253,7 @@
       </x:c>
       <x:c r="M14" s="4" t="n">
         <x:f>K14</x:f>
-        <x:v>5</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="N14" s="5" t="inlineStr">
         <x:is>
@@ -1247,10 +1272,10 @@
           <x:t xml:space="preserve">Ki</x:t>
         </x:is>
       </x:c>
-      <x:c r="C15" s="3" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D15" s="3" t="n">
+      <x:c r="C15" s="3">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D15" s="3">
         <x:v>1</x:v>
       </x:c>
       <x:c r="E15" s="3">
@@ -1261,7 +1286,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G15" s="4" t="n">
-        <x:f>IF(B15="Physical",POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7),POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7))</x:f>
+        <x:f>IF(B15="Physical",POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7),IF(B15="Hybrid",(POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7)+POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7))/2,POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="H15" s="4" t="n">
@@ -1274,11 +1299,11 @@
       </x:c>
       <x:c r="J15" s="4" t="n">
         <x:f>C15*F15*G15*Combatants!$O$5</x:f>
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="K15" s="4" t="n">
         <x:f>J15*D15</x:f>
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="L15" s="4" t="n">
         <x:f>0</x:f>
@@ -1286,10 +1311,12 @@
       </x:c>
       <x:c r="M15" s="4" t="n">
         <x:f>K15</x:f>
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="N15" s="5" t="str">
-        <x:v>Owner-immune; 50% decay after each landed pierce</x:v>
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="N15" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Owner-immune; 50% decay after each landed pierce</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -1303,10 +1330,10 @@
           <x:t xml:space="preserve">Ki</x:t>
         </x:is>
       </x:c>
-      <x:c r="C16" s="3" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D16" s="3" t="n">
+      <x:c r="C16" s="3">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D16" s="3">
         <x:v>2</x:v>
       </x:c>
       <x:c r="E16" s="3">
@@ -1317,7 +1344,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G16" s="4" t="n">
-        <x:f>IF(B16="Physical",POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7),POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7))</x:f>
+        <x:f>IF(B16="Physical",POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7),IF(B16="Hybrid",(POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7)+POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7))/2,POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="H16" s="4" t="n">
@@ -1330,11 +1357,11 @@
       </x:c>
       <x:c r="J16" s="4" t="n">
         <x:f>C16*F16*G16*Combatants!$O$5</x:f>
-        <x:v>6</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="K16" s="4" t="n">
         <x:f>J16*D16</x:f>
-        <x:v>12</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="L16" s="4" t="n">
         <x:f>0</x:f>
@@ -1342,10 +1369,12 @@
       </x:c>
       <x:c r="M16" s="4" t="n">
         <x:f>K16</x:f>
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="N16" s="5" t="str">
-        <x:v>Direct plus splash; owner-immune</x:v>
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="N16" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Direct plus splash; owner-immune</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -1360,7 +1389,7 @@
         </x:is>
       </x:c>
       <x:c r="C17" s="3">
-        <x:v>0.5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D17" s="3">
         <x:v>4</x:v>
@@ -1373,7 +1402,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G17" s="4" t="n">
-        <x:f>IF(B17="Physical",POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7),POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7))</x:f>
+        <x:f>IF(B17="Physical",POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7),IF(B17="Hybrid",(POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7)+POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7))/2,POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="H17" s="4" t="n">
@@ -1386,11 +1415,11 @@
       </x:c>
       <x:c r="J17" s="4" t="n">
         <x:f>C17*F17*G17*Combatants!$O$5</x:f>
-        <x:v>0.5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="K17" s="4" t="n">
         <x:f>J17*D17</x:f>
-        <x:v>2</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="L17" s="4" t="n">
         <x:f>0</x:f>
@@ -1398,7 +1427,7 @@
       </x:c>
       <x:c r="M17" s="4" t="n">
         <x:f>K17</x:f>
-        <x:v>2</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="N17" s="5" t="inlineStr">
         <x:is>
@@ -1417,10 +1446,10 @@
           <x:t xml:space="preserve">Ki</x:t>
         </x:is>
       </x:c>
-      <x:c r="C18" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D18" s="3" t="n">
+      <x:c r="C18" s="3">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="D18" s="3">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E18" s="3">
@@ -1431,7 +1460,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G18" s="4" t="n">
-        <x:f>IF(B18="Physical",POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7),POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7))</x:f>
+        <x:f>IF(B18="Physical",POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7),IF(B18="Hybrid",(POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7)+POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7))/2,POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="H18" s="4" t="n">
@@ -1444,11 +1473,11 @@
       </x:c>
       <x:c r="J18" s="4" t="n">
         <x:f>C18*F18*G18*Combatants!$O$5</x:f>
-        <x:v>1</x:v>
+        <x:v>1.5</x:v>
       </x:c>
       <x:c r="K18" s="4" t="n">
         <x:f>J18*D18</x:f>
-        <x:v>16</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="L18" s="4" t="n">
         <x:f>0</x:f>
@@ -1456,10 +1485,12 @@
       </x:c>
       <x:c r="M18" s="4" t="n">
         <x:f>K18</x:f>
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="N18" s="5" t="str">
-        <x:v>20 emissions; shared budget caps actual total at 16</x:v>
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="N18" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Shared budget 24</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -1474,10 +1505,10 @@
         </x:is>
       </x:c>
       <x:c r="C19" s="3">
-        <x:v>0.3</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D19" s="3">
-        <x:v>40</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E19" s="3">
         <x:v>0</x:v>
@@ -1487,7 +1518,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G19" s="4" t="n">
-        <x:f>IF(B19="Physical",POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7),POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7))</x:f>
+        <x:f>IF(B19="Physical",POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7),IF(B19="Hybrid",(POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7)+POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7))/2,POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="H19" s="4" t="n">
@@ -1500,11 +1531,11 @@
       </x:c>
       <x:c r="J19" s="4" t="n">
         <x:f>C19*F19*G19*Combatants!$O$5</x:f>
-        <x:v>0.3</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K19" s="4" t="n">
         <x:f>J19*D19</x:f>
-        <x:v>12</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="L19" s="4" t="n">
         <x:f>0</x:f>
@@ -1512,11 +1543,11 @@
       </x:c>
       <x:c r="M19" s="4" t="n">
         <x:f>K19</x:f>
-        <x:v>12</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="N19" s="5" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Budget caps actual total at 18</x:t>
+          <x:t xml:space="preserve">Maximum shared budget</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -1532,10 +1563,10 @@
         </x:is>
       </x:c>
       <x:c r="C20" s="3">
-        <x:v>0.4</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D20" s="3">
-        <x:v>20</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E20" s="3">
         <x:v>0</x:v>
@@ -1545,7 +1576,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G20" s="4" t="n">
-        <x:f>IF(B20="Physical",POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7),POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7))</x:f>
+        <x:f>IF(B20="Physical",POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7),IF(B20="Hybrid",(POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7)+POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7))/2,POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="H20" s="4" t="n">
@@ -1558,11 +1589,11 @@
       </x:c>
       <x:c r="J20" s="4" t="n">
         <x:f>C20*F20*G20*Combatants!$O$5</x:f>
-        <x:v>0.4</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="K20" s="4" t="n">
         <x:f>J20*D20</x:f>
-        <x:v>8</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="L20" s="4" t="n">
         <x:f>0</x:f>
@@ -1570,11 +1601,11 @@
       </x:c>
       <x:c r="M20" s="4" t="n">
         <x:f>K20</x:f>
-        <x:v>8</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="N20" s="5" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Budget caps actual total at 16</x:t>
+          <x:t xml:space="preserve">Maximum shared budget</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -1590,7 +1621,7 @@
         </x:is>
       </x:c>
       <x:c r="C21" s="3">
-        <x:v>0.2</x:v>
+        <x:v>0.75</x:v>
       </x:c>
       <x:c r="D21" s="3">
         <x:v>20</x:v>
@@ -1603,7 +1634,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G21" s="4" t="n">
-        <x:f>IF(B21="Physical",POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7),POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7))</x:f>
+        <x:f>IF(B21="Physical",POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7),IF(B21="Hybrid",(POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7)+POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7))/2,POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="H21" s="4" t="n">
@@ -1616,11 +1647,11 @@
       </x:c>
       <x:c r="J21" s="4" t="n">
         <x:f>C21*F21*G21*Combatants!$O$5</x:f>
-        <x:v>0.2</x:v>
+        <x:v>0.75</x:v>
       </x:c>
       <x:c r="K21" s="4" t="n">
         <x:f>J21*D21</x:f>
-        <x:v>4</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="L21" s="4" t="n">
         <x:f>0</x:f>
@@ -1628,11 +1659,11 @@
       </x:c>
       <x:c r="M21" s="4" t="n">
         <x:f>K21</x:f>
-        <x:v>4</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="N21" s="5" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Emission cap</x:t>
+          <x:t xml:space="preserve">Maximum 20 emissions</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -1661,7 +1692,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G22" s="4" t="n">
-        <x:f>IF(B22="Physical",POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7),POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7))</x:f>
+        <x:f>IF(B22="Physical",POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7),IF(B22="Hybrid",(POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7)+POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7))/2,POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="H22" s="4" t="n">
@@ -1688,8 +1719,10 @@
         <x:f>K22</x:f>
         <x:v>52</x:v>
       </x:c>
-      <x:c r="N22" s="5" t="str">
-        <x:v>Lock uncapped; explosive budget 52</x:v>
+      <x:c r="N22" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Lock uncapped; explosive budget 52</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -1704,7 +1737,7 @@
         </x:is>
       </x:c>
       <x:c r="C23" s="3">
-        <x:v>4</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D23" s="3">
         <x:v>1</x:v>
@@ -1717,7 +1750,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G23" s="4" t="n">
-        <x:f>IF(B23="Physical",POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7),POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7))</x:f>
+        <x:f>IF(B23="Physical",POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7),IF(B23="Hybrid",(POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7)+POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7))/2,POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="H23" s="4" t="n">
@@ -1730,11 +1763,11 @@
       </x:c>
       <x:c r="J23" s="4" t="n">
         <x:f>C23*F23*G23*Combatants!$O$5</x:f>
-        <x:v>4</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="K23" s="4" t="n">
         <x:f>J23*D23</x:f>
-        <x:v>4</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="L23" s="4" t="n">
         <x:f>0</x:f>
@@ -1742,10 +1775,12 @@
       </x:c>
       <x:c r="M23" s="4" t="n">
         <x:f>K23</x:f>
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="N23" s="5" t="str">
-        <x:v>Lock uncapped; explosive budget 4</x:v>
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="N23" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Lock uncapped; explosive budget 12</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -1760,7 +1795,7 @@
         </x:is>
       </x:c>
       <x:c r="C24" s="3">
-        <x:v>3</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D24" s="3">
         <x:v>1</x:v>
@@ -1773,7 +1808,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G24" s="4" t="n">
-        <x:f>IF(B24="Physical",POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7),POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7))</x:f>
+        <x:f>IF(B24="Physical",POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7),IF(B24="Hybrid",(POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7)+POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7))/2,POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="H24" s="4" t="n">
@@ -1786,11 +1821,11 @@
       </x:c>
       <x:c r="J24" s="4" t="n">
         <x:f>C24*F24*G24*Combatants!$O$5</x:f>
-        <x:v>3</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="K24" s="4" t="n">
         <x:f>J24*D24</x:f>
-        <x:v>3</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="L24" s="4" t="n">
         <x:f>0</x:f>
@@ -1798,10 +1833,12 @@
       </x:c>
       <x:c r="M24" s="4" t="n">
         <x:f>K24</x:f>
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="N24" s="5" t="str">
-        <x:v>Lock uncapped; explosive budget 3</x:v>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="N24" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Lock uncapped; explosive budget 10</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -1816,7 +1853,7 @@
         </x:is>
       </x:c>
       <x:c r="C25" s="3">
-        <x:v>3</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D25" s="3">
         <x:v>1</x:v>
@@ -1829,7 +1866,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G25" s="4" t="n">
-        <x:f>IF(B25="Physical",POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7),POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7))</x:f>
+        <x:f>IF(B25="Physical",POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7),IF(B25="Hybrid",(POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7)+POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7))/2,POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="H25" s="4" t="n">
@@ -1842,11 +1879,11 @@
       </x:c>
       <x:c r="J25" s="4" t="n">
         <x:f>C25*F25*G25*Combatants!$O$5</x:f>
-        <x:v>3</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="K25" s="4" t="n">
         <x:f>J25*D25</x:f>
-        <x:v>3</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="L25" s="4" t="n">
         <x:f>0</x:f>
@@ -1854,10 +1891,12 @@
       </x:c>
       <x:c r="M25" s="4" t="n">
         <x:f>K25</x:f>
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="N25" s="5" t="str">
-        <x:v>Lock uncapped; explosive budget 3</x:v>
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="N25" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Lock uncapped; explosive budget 12</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -1872,7 +1911,7 @@
         </x:is>
       </x:c>
       <x:c r="C26" s="3">
-        <x:v>5</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D26" s="3">
         <x:v>1</x:v>
@@ -1885,7 +1924,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G26" s="4" t="n">
-        <x:f>IF(B26="Physical",POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7),POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7))</x:f>
+        <x:f>IF(B26="Physical",POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7),IF(B26="Hybrid",(POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7)+POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7))/2,POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="H26" s="4" t="n">
@@ -1898,11 +1937,11 @@
       </x:c>
       <x:c r="J26" s="4" t="n">
         <x:f>C26*F26*G26*Combatants!$O$5</x:f>
-        <x:v>5</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="K26" s="4" t="n">
         <x:f>J26*D26</x:f>
-        <x:v>5</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="L26" s="4" t="n">
         <x:f>0</x:f>
@@ -1910,10 +1949,12 @@
       </x:c>
       <x:c r="M26" s="4" t="n">
         <x:f>K26</x:f>
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="N26" s="5" t="str">
-        <x:v>Lock uncapped; explosive budget 5</x:v>
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="N26" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Lock uncapped; explosive budget 16</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -1928,7 +1969,7 @@
         </x:is>
       </x:c>
       <x:c r="C27" s="3">
-        <x:v>8</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D27" s="3">
         <x:v>1</x:v>
@@ -1941,7 +1982,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G27" s="4" t="n">
-        <x:f>IF(B27="Physical",POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7),POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7))</x:f>
+        <x:f>IF(B27="Physical",POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7),IF(B27="Hybrid",(POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7)+POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7))/2,POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="H27" s="4" t="n">
@@ -1954,11 +1995,11 @@
       </x:c>
       <x:c r="J27" s="4" t="n">
         <x:f>C27*F27*G27*Combatants!$O$5</x:f>
-        <x:v>8</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="K27" s="4" t="n">
         <x:f>J27*D27</x:f>
-        <x:v>8</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="L27" s="4" t="n">
         <x:f>0</x:f>
@@ -1966,10 +2007,12 @@
       </x:c>
       <x:c r="M27" s="4" t="n">
         <x:f>K27</x:f>
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="N27" s="5" t="str">
-        <x:v>Lock uncapped; explosive budget 8</x:v>
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="N27" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Lock uncapped; explosive budget 18</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -1984,7 +2027,7 @@
         </x:is>
       </x:c>
       <x:c r="C28" s="3">
-        <x:v>5</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D28" s="3">
         <x:v>1</x:v>
@@ -1997,7 +2040,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G28" s="4" t="n">
-        <x:f>IF(B28="Physical",POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7),POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7))</x:f>
+        <x:f>IF(B28="Physical",POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7),IF(B28="Hybrid",(POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7)+POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7))/2,POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="H28" s="4" t="n">
@@ -2010,11 +2053,11 @@
       </x:c>
       <x:c r="J28" s="4" t="n">
         <x:f>C28*F28*G28*Combatants!$O$5</x:f>
-        <x:v>5</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="K28" s="4" t="n">
         <x:f>J28*D28</x:f>
-        <x:v>5</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="L28" s="4" t="n">
         <x:f>0</x:f>
@@ -2022,10 +2065,12 @@
       </x:c>
       <x:c r="M28" s="4" t="n">
         <x:f>K28</x:f>
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="N28" s="5" t="str">
-        <x:v>Lock uncapped; explosive budget 5</x:v>
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="N28" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Lock uncapped; explosive budget 13</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="29">
@@ -2040,7 +2085,7 @@
         </x:is>
       </x:c>
       <x:c r="C29" s="3">
-        <x:v>12</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D29" s="3">
         <x:v>1</x:v>
@@ -2053,7 +2098,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G29" s="4" t="n">
-        <x:f>IF(B29="Physical",POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7),POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7))</x:f>
+        <x:f>IF(B29="Physical",POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7),IF(B29="Hybrid",(POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7)+POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7))/2,POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="H29" s="4" t="n">
@@ -2066,11 +2111,11 @@
       </x:c>
       <x:c r="J29" s="4" t="n">
         <x:f>C29*F29*G29*Combatants!$O$5</x:f>
-        <x:v>12</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="K29" s="4" t="n">
         <x:f>J29*D29</x:f>
-        <x:v>12</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="L29" s="4" t="n">
         <x:f>0</x:f>
@@ -2078,10 +2123,12 @@
       </x:c>
       <x:c r="M29" s="4" t="n">
         <x:f>K29</x:f>
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="N29" s="5" t="str">
-        <x:v>Lock uncapped; explosive budget 12</x:v>
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="N29" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Lock uncapped; explosive budget 24</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="30">
@@ -2096,7 +2143,7 @@
         </x:is>
       </x:c>
       <x:c r="C30" s="3">
-        <x:v>7</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D30" s="3">
         <x:v>1</x:v>
@@ -2109,7 +2156,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G30" s="4" t="n">
-        <x:f>IF(B30="Physical",POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7),POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7))</x:f>
+        <x:f>IF(B30="Physical",POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7),IF(B30="Hybrid",(POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7)+POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7))/2,POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="H30" s="4" t="n">
@@ -2122,11 +2169,11 @@
       </x:c>
       <x:c r="J30" s="4" t="n">
         <x:f>C30*F30*G30*Combatants!$O$5</x:f>
-        <x:v>7</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="K30" s="4" t="n">
         <x:f>J30*D30</x:f>
-        <x:v>7</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="L30" s="4" t="n">
         <x:f>0</x:f>
@@ -2134,10 +2181,12 @@
       </x:c>
       <x:c r="M30" s="4" t="n">
         <x:f>K30</x:f>
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="N30" s="5" t="str">
-        <x:v>Lock uncapped; explosive budget 7</x:v>
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="N30" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Lock uncapped; explosive budget 17</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="31">
@@ -2152,7 +2201,7 @@
         </x:is>
       </x:c>
       <x:c r="C31" s="3">
-        <x:v>6</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D31" s="3">
         <x:v>1</x:v>
@@ -2165,7 +2214,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G31" s="4" t="n">
-        <x:f>IF(B31="Physical",POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7),POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7))</x:f>
+        <x:f>IF(B31="Physical",POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7),IF(B31="Hybrid",(POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7)+POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7))/2,POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="H31" s="4" t="n">
@@ -2178,11 +2227,11 @@
       </x:c>
       <x:c r="J31" s="4" t="n">
         <x:f>C31*F31*G31*Combatants!$O$5</x:f>
-        <x:v>6</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K31" s="4" t="n">
         <x:f>J31*D31</x:f>
-        <x:v>6</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="L31" s="4" t="n">
         <x:f>0</x:f>
@@ -2190,166 +2239,824 @@
       </x:c>
       <x:c r="M31" s="4" t="n">
         <x:f>K31</x:f>
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="N31" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Lock uncapped; explosive budget 15</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Dragon Nova</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B32" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Ki</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C32" s="3">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D32" s="3">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E32" s="3">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F32" s="4" t="n">
+        <x:f>POWER(Combatants!$E$4/Combatants!$E$5,Settings!$B$6)</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G32" s="4" t="n">
+        <x:f>IF(B32="Physical",POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7),IF(B32="Hybrid",(POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7)+POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7))/2,POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7)))</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H32" s="4" t="n">
+        <x:f>1</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I32" s="4" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J32" s="4" t="n">
+        <x:f>C32*F32*G32*Combatants!$O$5</x:f>
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="K32" s="4" t="n">
+        <x:f>J32*D32</x:f>
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="L32" s="4" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M32" s="4" t="n">
+        <x:f>K32</x:f>
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="N32" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Direct plus equal splash</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Sky Break</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B33" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Physical</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C33" s="3">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D33" s="3">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E33" s="3">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F33" s="4" t="n">
+        <x:f>POWER(Combatants!$E$4/Combatants!$E$5,Settings!$B$6)</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G33" s="4" t="n">
+        <x:f>IF(B33="Physical",POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7),IF(B33="Hybrid",(POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7)+POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7))/2,POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7)))</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H33" s="4" t="n">
+        <x:f>1</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I33" s="4" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J33" s="4" t="n">
+        <x:f>C33*F33*G33*Combatants!$O$5</x:f>
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="K33" s="4" t="n">
+        <x:f>J33*D33</x:f>
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="L33" s="4" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M33" s="4" t="n">
+        <x:f>K33</x:f>
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="N33" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Strength-scaled direct plus splash</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Echoing Slash</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B34" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Physical</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C34" s="3">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D34" s="3">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E34" s="3">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F34" s="4" t="n">
+        <x:f>POWER(Combatants!$E$4/Combatants!$E$5,Settings!$B$6)</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G34" s="4" t="n">
+        <x:f>IF(B34="Physical",POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7),IF(B34="Hybrid",(POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7)+POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7))/2,POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7)))</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H34" s="4" t="n">
+        <x:f>1</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I34" s="4" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J34" s="4" t="n">
+        <x:f>C34*F34*G34*Combatants!$O$5</x:f>
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="K34" s="4" t="n">
+        <x:f>J34*D34</x:f>
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="L34" s="4" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M34" s="4" t="n">
+        <x:f>K34</x:f>
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="N34" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Strength-scaled cutting wave</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Explosion</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B35" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Ki</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C35" s="3">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D35" s="3">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E35" s="3">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F35" s="4" t="n">
+        <x:f>POWER(Combatants!$E$4/Combatants!$E$5,Settings!$B$6)</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G35" s="4" t="n">
+        <x:f>IF(B35="Physical",POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7),IF(B35="Hybrid",(POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7)+POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7))/2,POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7)))</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H35" s="4" t="n">
+        <x:f>1</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I35" s="4" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J35" s="4" t="n">
+        <x:f>C35*F35*G35*Combatants!$O$5</x:f>
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="K35" s="4" t="n">
+        <x:f>J35*D35</x:f>
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="L35" s="4" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M35" s="4" t="n">
+        <x:f>K35</x:f>
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="N35" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Aimed area hit</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Shockwave</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B36" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Hybrid</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C36" s="3">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="D36" s="3">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E36" s="3">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F36" s="4" t="n">
+        <x:f>POWER(Combatants!$E$4/Combatants!$E$5,Settings!$B$6)</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G36" s="4" t="n">
+        <x:f>IF(B36="Physical",POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7),IF(B36="Hybrid",(POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7)+POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7))/2,POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7)))</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H36" s="4" t="n">
+        <x:f>1</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I36" s="4" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J36" s="4" t="n">
+        <x:f>C36*F36*G36*Combatants!$O$5</x:f>
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="K36" s="4" t="n">
+        <x:f>J36*D36</x:f>
+        <x:v>10.5</x:v>
+      </x:c>
+      <x:c r="L36" s="4" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M36" s="4" t="n">
+        <x:f>K36</x:f>
+        <x:v>10.5</x:v>
+      </x:c>
+      <x:c r="N36" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Seven pulses</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Kikoho</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B37" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Ki</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C37" s="3">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="D37" s="3">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E37" s="3">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F37" s="4" t="n">
+        <x:f>POWER(Combatants!$E$4/Combatants!$E$5,Settings!$B$6)</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G37" s="4" t="n">
+        <x:f>IF(B37="Physical",POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7),IF(B37="Hybrid",(POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7)+POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7))/2,POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7)))</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H37" s="4" t="n">
+        <x:f>1</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I37" s="4" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J37" s="4" t="n">
+        <x:f>C37*F37*G37*Combatants!$O$5</x:f>
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="K37" s="4" t="n">
+        <x:f>J37*D37</x:f>
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="L37" s="4" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M37" s="4" t="n">
+        <x:f>K37</x:f>
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="N37" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">6% self-damage pool</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Death Ball - Full</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B38" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Ki</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C38" s="3">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D38" s="3">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E38" s="3">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F38" s="4" t="n">
+        <x:f>POWER(Combatants!$E$4/Combatants!$E$5,Settings!$B$6)</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G38" s="4" t="n">
+        <x:f>IF(B38="Physical",POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7),IF(B38="Hybrid",(POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7)+POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7))/2,POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7)))</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H38" s="4" t="n">
+        <x:f>1</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I38" s="4" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J38" s="4" t="n">
+        <x:f>C38*F38*G38*Combatants!$O$5</x:f>
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="K38" s="4" t="n">
+        <x:f>J38*D38</x:f>
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="L38" s="4" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M38" s="4" t="n">
+        <x:f>K38</x:f>
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="N38" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Full charge</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Supernova - Full</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B39" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Ki</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C39" s="3">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D39" s="3">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E39" s="3">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F39" s="4" t="n">
+        <x:f>POWER(Combatants!$E$4/Combatants!$E$5,Settings!$B$6)</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G39" s="4" t="n">
+        <x:f>IF(B39="Physical",POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7),IF(B39="Hybrid",(POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7)+POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7))/2,POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7)))</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H39" s="4" t="n">
+        <x:f>1</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I39" s="4" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J39" s="4" t="n">
+        <x:f>C39*F39*G39*Combatants!$O$5</x:f>
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="K39" s="4" t="n">
+        <x:f>J39*D39</x:f>
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="L39" s="4" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M39" s="4" t="n">
+        <x:f>K39</x:f>
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="N39" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Full-charge direct plus splash</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Final Explosion - Full</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B40" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Ki</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C40" s="3">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D40" s="3">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E40" s="3">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F40" s="4" t="n">
+        <x:f>POWER(Combatants!$E$4/Combatants!$E$5,Settings!$B$6)</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G40" s="4" t="n">
+        <x:f>IF(B40="Physical",POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7),IF(B40="Hybrid",(POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7)+POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7))/2,POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7)))</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H40" s="4" t="n">
+        <x:f>1</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I40" s="4" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J40" s="4" t="n">
+        <x:f>C40*F40*G40*Combatants!$O$5</x:f>
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="K40" s="4" t="n">
+        <x:f>J40*D40</x:f>
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="L40" s="4" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M40" s="4" t="n">
+        <x:f>K40</x:f>
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="N40" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Full charge in five stacks</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Self Destruct</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B41" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Ki</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C41" s="3">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="D41" s="3">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E41" s="3">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F41" s="4" t="n">
+        <x:f>POWER(Combatants!$E$4/Combatants!$E$5,Settings!$B$6)</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G41" s="4" t="n">
+        <x:f>IF(B41="Physical",POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7),IF(B41="Hybrid",(POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7)+POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7))/2,POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7)))</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H41" s="4" t="n">
+        <x:f>1</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I41" s="4" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J41" s="4" t="n">
+        <x:f>C41*F41*G41*Combatants!$O$5</x:f>
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="K41" s="4" t="n">
+        <x:f>J41*D41</x:f>
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="L41" s="4" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M41" s="4" t="n">
+        <x:f>K41</x:f>
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="N41" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Caster dies</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Wall of Flame</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B42" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Ki</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C42" s="3">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D42" s="3">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="N31" s="5" t="str">
-        <x:v>Lock uncapped; explosive budget 6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32">
-      <x:c r="A32" t="str">
-        <x:v>Dragon Nova</x:v>
-      </x:c>
-      <x:c r="B32" t="str">
-        <x:v>Ki</x:v>
-      </x:c>
-      <x:c r="C32" t="n">
+      <x:c r="E42" s="3">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F42" s="4" t="n">
+        <x:f>POWER(Combatants!$E$4/Combatants!$E$5,Settings!$B$6)</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G42" s="4" t="n">
+        <x:f>IF(B42="Physical",POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7),IF(B42="Hybrid",(POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7)+POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7))/2,POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7)))</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H42" s="4" t="n">
+        <x:f>1</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I42" s="4" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J42" s="4" t="n">
+        <x:f>C42*F42*G42*Combatants!$O$5</x:f>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K42" s="4" t="n">
+        <x:f>J42*D42</x:f>
         <x:v>12</x:v>
       </x:c>
-      <x:c r="D32" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="E32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F32" t="n">
+      <x:c r="L42" s="4" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M42" s="4" t="n">
+        <x:f>K42</x:f>
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="N42" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Maximum six pulses</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Super Ghost Kamikaze</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B43" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Ki</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C43" s="3">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D43" s="3">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E43" s="3">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F43" s="4" t="n">
         <x:f>POWER(Combatants!$E$4/Combatants!$E$5,Settings!$B$6)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G32" t="n">
-        <x:f>IF(B32="Physical",POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7),POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7))</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H32" t="n">
+      <x:c r="G43" s="4" t="n">
+        <x:f>IF(B43="Physical",POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7),IF(B43="Hybrid",(POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7)+POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7))/2,POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7)))</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H43" s="4" t="n">
         <x:f>1</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I32" t="n">
+      <x:c r="I43" s="4" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J32" t="n">
-        <x:f>C32*F32*G32*Combatants!$O$5</x:f>
+      <x:c r="J43" s="4" t="n">
+        <x:f>C43*F43*G43*Combatants!$O$5</x:f>
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="K43" s="4" t="n">
+        <x:f>J43*D43</x:f>
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="L43" s="4" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M43" s="4" t="n">
+        <x:f>K43</x:f>
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="N43" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Three homing ghosts</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Fireball</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B44" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Ki</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C44" s="3">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D44" s="3">
+        <x:v>1.7</x:v>
+      </x:c>
+      <x:c r="E44" s="3">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F44" s="4" t="n">
+        <x:f>POWER(Combatants!$E$4/Combatants!$E$5,Settings!$B$6)</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G44" s="4" t="n">
+        <x:f>IF(B44="Physical",POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7),IF(B44="Hybrid",(POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7)+POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7))/2,POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7)))</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H44" s="4" t="n">
+        <x:f>1</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I44" s="4" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J44" s="4" t="n">
+        <x:f>C44*F44*G44*Combatants!$O$5</x:f>
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="K44" s="4" t="n">
+        <x:f>J44*D44</x:f>
+        <x:v>13.6</x:v>
+      </x:c>
+      <x:c r="L44" s="4" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M44" s="4" t="n">
+        <x:f>K44</x:f>
+        <x:v>13.6</x:v>
+      </x:c>
+      <x:c r="N44" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Direct plus 70% splash</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Frost Nova</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B45" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Ki</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C45" s="3">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="K32" t="n">
-        <x:f>J32*D32</x:f>
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="L32" t="n">
+      <x:c r="D45" s="3">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E45" s="3">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F45" s="4" t="n">
+        <x:f>POWER(Combatants!$E$4/Combatants!$E$5,Settings!$B$6)</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G45" s="4" t="n">
+        <x:f>IF(B45="Physical",POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7),IF(B45="Hybrid",(POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7)+POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7))/2,POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7)))</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H45" s="4" t="n">
+        <x:f>1</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I45" s="4" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M32" t="n">
-        <x:f>K32</x:f>
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="N32" t="str">
-        <x:v>Direct plus equal splash</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33">
-      <x:c r="A33" t="str">
-        <x:v>Sky Break</x:v>
-      </x:c>
-      <x:c r="B33" t="str">
-        <x:v>Physical</x:v>
-      </x:c>
-      <x:c r="C33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="E33" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F33" t="n">
-        <x:f>POWER(Combatants!$E$4/Combatants!$E$5,Settings!$B$6)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G33" t="n">
-        <x:f>IF(B33="Physical",POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7),POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7))</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H33" t="n">
-        <x:f>1</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I33" t="n">
+      <x:c r="J45" s="4" t="n">
+        <x:f>C45*F45*G45*Combatants!$O$5</x:f>
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="K45" s="4" t="n">
+        <x:f>J45*D45</x:f>
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="L45" s="4" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J33" t="n">
-        <x:f>C33*F33*G33*Combatants!$O$5</x:f>
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="K33" t="n">
-        <x:f>J33*D33</x:f>
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="L33" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M33" t="n">
-        <x:f>K33</x:f>
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="N33" t="str">
-        <x:v>Strength-scaled direct plus splash</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34">
-      <x:c r="A34" t="str">
-        <x:v>Echoing Slash</x:v>
-      </x:c>
-      <x:c r="B34" t="str">
-        <x:v>Physical</x:v>
-      </x:c>
-      <x:c r="C34" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E34" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F34" t="n">
-        <x:f>POWER(Combatants!$E$4/Combatants!$E$5,Settings!$B$6)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G34" t="n">
-        <x:f>IF(B34="Physical",POWER(2*Combatants!$H$4/(Combatants!$H$4+Combatants!$I$5),Settings!$B$7),POWER(2*Combatants!$J$4/(Combatants!$J$4+Combatants!$K$5),Settings!$B$7))</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H34" t="n">
-        <x:f>1</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I34" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J34" t="n">
-        <x:f>C34*F34*G34*Combatants!$O$5</x:f>
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="K34" t="n">
-        <x:f>J34*D34</x:f>
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="L34" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M34" t="n">
-        <x:f>K34</x:f>
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="N34" t="str">
-        <x:v>Strength-scaled cutting wave</x:v>
+      <x:c r="M45" s="4" t="n">
+        <x:f>K45</x:f>
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="N45" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Two-tile area</x:t>
+        </x:is>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2361,7 +3068,7 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="42" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="42" customWidth="1"/>
     <x:col min="2" max="2" width="18" customWidth="1"/>
     <x:col min="3" max="3" width="18" customWidth="1"/>
     <x:col min="4" max="4" width="18" customWidth="1"/>
@@ -2437,11 +3144,11 @@
         </x:is>
       </x:c>
       <x:c r="B4">
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C4" s="4" t="n">
         <x:f>'Damage Calculator'!J5</x:f>
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D4" s="4" t="n">
         <x:f>C4-B4</x:f>
@@ -2459,12 +3166,12 @@
           <x:t xml:space="preserve">Wolf Fang per hit</x:t>
         </x:is>
       </x:c>
-      <x:c r="B5" t="n">
-        <x:v>2</x:v>
+      <x:c r="B5">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C5" s="4" t="n">
         <x:f>'Damage Calculator'!J6</x:f>
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D5" s="4" t="n">
         <x:f>C5-B5</x:f>
@@ -2482,12 +3189,12 @@
           <x:t xml:space="preserve">Wolf Fang five hits</x:t>
         </x:is>
       </x:c>
-      <x:c r="B6" t="n">
-        <x:v>10</x:v>
+      <x:c r="B6">
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C6" s="4" t="n">
         <x:f>'Damage Calculator'!J6*5</x:f>
-        <x:v>10</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D6" s="4" t="n">
         <x:f>C6-B6</x:f>
@@ -2505,12 +3212,12 @@
           <x:t xml:space="preserve">Hundred Crack per hit</x:t>
         </x:is>
       </x:c>
-      <x:c r="B7" t="n">
-        <x:v>0.5</x:v>
+      <x:c r="B7">
+        <x:v>0.75</x:v>
       </x:c>
       <x:c r="C7" s="4" t="n">
         <x:f>'Damage Calculator'!J7</x:f>
-        <x:v>0.5</x:v>
+        <x:v>0.75</x:v>
       </x:c>
       <x:c r="D7" s="4" t="n">
         <x:f>C7-B7</x:f>
@@ -2528,12 +3235,12 @@
           <x:t xml:space="preserve">Hundred Crack minimum total</x:t>
         </x:is>
       </x:c>
-      <x:c r="B8" t="n">
-        <x:v>12</x:v>
+      <x:c r="B8">
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C8" s="4" t="n">
         <x:f>'Damage Calculator'!J7*24</x:f>
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D8" s="4" t="n">
         <x:f>C8-B8</x:f>
@@ -2551,12 +3258,12 @@
           <x:t xml:space="preserve">Rock Throw powerful</x:t>
         </x:is>
       </x:c>
-      <x:c r="B9" t="n">
-        <x:v>3.5</x:v>
+      <x:c r="B9">
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C9" s="4" t="n">
         <x:f>'Damage Calculator'!J8</x:f>
-        <x:v>3.5</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D9" s="4" t="n">
         <x:f>C9-B9</x:f>
@@ -2575,11 +3282,11 @@
         </x:is>
       </x:c>
       <x:c r="B10">
-        <x:v>8</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C10" s="4" t="n">
         <x:f>'Damage Calculator'!J13*2</x:f>
-        <x:v>8</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D10" s="4" t="n">
         <x:f>C10-B10</x:f>
@@ -2587,7 +3294,7 @@
       </x:c>
       <x:c r="E10" s="5" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4 x2</x:t>
+          <x:t xml:space="preserve">8 x2</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -2598,11 +3305,11 @@
         </x:is>
       </x:c>
       <x:c r="B11">
-        <x:v>44</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C11" s="4" t="n">
         <x:f>'Damage Calculator'!J12*2</x:f>
-        <x:v>44</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D11" s="4" t="n">
         <x:f>C11-B11</x:f>
@@ -2610,84 +3317,123 @@
       </x:c>
       <x:c r="E11" s="5" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">22 x2</x:t>
+          <x:t xml:space="preserve">28 x2</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" t="str">
-        <x:v>Dragon Nova direct plus splash</x:v>
-      </x:c>
-      <x:c r="B12" t="n">
+      <x:c r="A12" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Dragon Nova direct plus splash</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B12">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C12" s="4" t="n">
+        <x:f>'Damage Calculator'!J32*2</x:f>
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D12" s="4" t="n">
+        <x:f>C12-B12</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E12" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">18 x2</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Sky Break direct plus splash</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B13">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C13" s="4" t="n">
+        <x:f>'Damage Calculator'!J33*2</x:f>
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="D13" s="4" t="n">
+        <x:f>C13-B13</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E13" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">13 x2</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Echoing Slash</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B14">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C14" s="4" t="n">
+        <x:f>'Damage Calculator'!J34</x:f>
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D14" s="4" t="n">
+        <x:f>C14-B14</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E14" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Strength-scaled factor</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Kikoho target hit</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B15">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C12" t="n">
-        <x:f>'Damage Calculator'!J32*2</x:f>
+      <x:c r="C15" s="4" t="n">
+        <x:f>'Damage Calculator'!J37</x:f>
         <x:v>24</x:v>
       </x:c>
-      <x:c r="D12" t="n">
-        <x:f>C12-B12</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E12" t="str">
-        <x:v>12 x2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13">
-      <x:c r="A13" t="str">
-        <x:v>Sky Break direct plus splash</x:v>
-      </x:c>
-      <x:c r="B13" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C13" t="n">
-        <x:f>'Damage Calculator'!J33*2</x:f>
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D13" t="n">
-        <x:f>C13-B13</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E13" t="str">
-        <x:v>8 x2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14">
-      <x:c r="A14" t="str">
-        <x:v>Echoing Slash</x:v>
-      </x:c>
-      <x:c r="B14" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C14" t="n">
-        <x:f>'Damage Calculator'!J34</x:f>
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D14" t="n">
-        <x:f>C14-B14</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E14" t="str">
-        <x:v>Strength-scaled factor</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15">
-      <x:c r="A15" t="str">
-        <x:v>Standard Beam at 13000 BP vs 200 BP</x:v>
-      </x:c>
-      <x:c r="B15" t="n">
-        <x:v>195</x:v>
-      </x:c>
-      <x:c r="C15" t="n">
-        <x:f>3*POWER(13000/200,Settings!$B$6)</x:f>
-        <x:v>195</x:v>
-      </x:c>
-      <x:c r="D15" t="n">
+      <x:c r="D15" s="4" t="n">
         <x:f>C15-B15</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E15" t="str">
-        <x:v>Linear BP scaling makes a 65x advantage immediately decisive</x:v>
+      <x:c r="E15" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Target factor; self pool is only 6%</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Standard Beam at 13000 BP vs 200 BP</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B16">
+        <x:v>650</x:v>
+      </x:c>
+      <x:c r="C16" s="4" t="n">
+        <x:f>10*POWER(13000/200,Settings!$B$6)</x:f>
+        <x:v>650</x:v>
+      </x:c>
+      <x:c r="D16" s="4" t="n">
+        <x:f>C16-B16</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E16" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Linear BP scaling makes a 65x advantage immediately decisive</x:t>
+        </x:is>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2802,154 +3548,202 @@
     <x:row r="9">
       <x:c r="A9" s="5" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">src/Code/ProjectileSystem/Blasts.dm</x:t>
+          <x:t xml:space="preserve">src/Code/ProjectileSystem/NexusBeams.dm</x:t>
         </x:is>
       </x:c>
       <x:c r="B9" s="5" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Projectile skill parameters and normalized 0.5ds Ki cadence</x:t>
+          <x:t xml:space="preserve">Integrated beam factors, range, drain and shield-pierce profiles</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="5" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">src/Code/Application/Combat/SkillEngine.dm</x:t>
+          <x:t xml:space="preserve">src/Code/ProjectileSystem/Blasts.dm</x:t>
         </x:is>
       </x:c>
       <x:c r="B10" s="5" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Current cast paths, projectile percentages and melee special routing</x:t>
+          <x:t xml:space="preserve">Projectile skill parameters and normalized 0.5ds Ki cadence</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="5" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">src/Code/Application/Combat/SkillControllers.dm</x:t>
+          <x:t xml:space="preserve">src/Code/Application/Combat/SkillEngine.dm</x:t>
         </x:is>
       </x:c>
       <x:c r="B11" s="5" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Sokidan/Kienzan guided movement</x:t>
+          <x:t xml:space="preserve">Current cast paths, projectile percentages and melee special routing</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="5" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">src/Code/Combat/RockThrow.dm</x:t>
+          <x:t xml:space="preserve">src/Code/Application/Combat/SkillControllers.dm</x:t>
         </x:is>
       </x:c>
       <x:c r="B12" s="5" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Rock skill damage, cost, cooldown and targeting</x:t>
+          <x:t xml:space="preserve">Sokidan/Kienzan guided movement</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="5" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">src/Code/Combat/HokutoShinken.dm</x:t>
+          <x:t xml:space="preserve">src/Code/Combat/NexusMeleeTechniques.dm</x:t>
         </x:is>
       </x:c>
       <x:c r="B13" s="5" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Hundred Crack Fist hit count and per-hit multiplier</x:t>
+          <x:t xml:space="preserve">Integrated weapon and Unarmed technique damage budgets</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="5" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">src/Code/BackgroundCode/StatLoop.dm</x:t>
+          <x:t xml:space="preserve">src/Code/Combat/NexusSpecialStyles.dm</x:t>
         </x:is>
       </x:c>
       <x:c r="B14" s="5" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">get_bp ordering, powerup, anger, cyber and late multipliers</x:t>
+          <x:t xml:space="preserve">Charged projectiles, persistent fields, area attacks and ghosts</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="5" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">src/Code/Technology/Cybernetics.dm</x:t>
+          <x:t xml:space="preserve">src/Code/Combat/RockThrow.dm</x:t>
         </x:is>
       </x:c>
       <x:c r="B15" s="5" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Module stat effects, Overdrive and cyber skill grants</x:t>
+          <x:t xml:space="preserve">Rock skill damage, cost, cooldown and targeting</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="5" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">src/Code/CharacterCreation/NexusCharacterCreation.dm</x:t>
+          <x:t xml:space="preserve">src/Code/Combat/HokutoShinken.dm</x:t>
         </x:is>
       </x:c>
       <x:c r="B16" s="5" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Race creation budgets and presets</x:t>
+          <x:t xml:space="preserve">Hundred Crack Fist hit count and per-hit multiplier</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="5" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">src/Code/CoreFunctions/StatPoints.dm</x:t>
+          <x:t xml:space="preserve">src/Code/BackgroundCode/StatLoop.dm</x:t>
         </x:is>
       </x:c>
       <x:c r="B17" s="5" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Race caps and additional profile data</x:t>
+          <x:t xml:space="preserve">get_bp ordering, powerup, anger, cyber and late multipliers</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="5" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">src/Code/PlayerMechanics/Ascension.dm</x:t>
+          <x:t xml:space="preserve">src/Code/Technology/Cybernetics.dm</x:t>
         </x:is>
       </x:c>
       <x:c r="B18" s="5" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SSJ, USSJ, Third Eye and Frost form effects</x:t>
+          <x:t xml:space="preserve">Module stat effects, Overdrive and cyber skill grants</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="5" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">src/Code/PlayerMechanics/GodKi.dm</x:t>
+          <x:t xml:space="preserve">src/Code/Technology/NexusMagic.dm</x:t>
         </x:is>
       </x:c>
       <x:c r="B19" s="5" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">God BP formula and mastery scaling</x:t>
+          <x:t xml:space="preserve">Arcane projectile and area spell damage</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="5" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">src/Code/Races/UltraInstinct.dm</x:t>
+          <x:t xml:space="preserve">src/Code/CharacterCreation/NexusCharacterCreation.dm</x:t>
         </x:is>
       </x:c>
       <x:c r="B20" s="5" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Ultra Instinct BP/stat/cost effects</x:t>
+          <x:t xml:space="preserve">Race creation budgets and presets</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="5" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">src/Code/CoreFunctions/StatPoints.dm</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B21" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Race caps and additional profile data</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">src/Code/PlayerMechanics/Ascension.dm</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B22" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SSJ, USSJ, Third Eye and Frost form effects</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">src/Code/PlayerMechanics/GodKi.dm</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B23" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">God BP formula and mastery scaling</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">src/Code/Races/UltraInstinct.dm</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B24" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Ultra Instinct BP/stat/cost effects</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="5" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">src/Code/Combat/KiSkills</x:t>
         </x:is>
       </x:c>
-      <x:c r="B21" s="5" t="inlineStr">
+      <x:c r="B25" s="5" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Spirit Bomb family, Kikoho, Final Explosion and Hakai custom formulas</x:t>
         </x:is>
@@ -3080,7 +3874,7 @@
           <x:t xml:space="preserve">BP exponent</x:t>
         </x:is>
       </x:c>
-      <x:c r="B6" s="3" t="n">
+      <x:c r="B6" s="3">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C6" t="inlineStr">
@@ -3088,8 +3882,10 @@
           <x:t xml:space="preserve">ratio exponent</x:t>
         </x:is>
       </x:c>
-      <x:c r="D6" s="5" t="str">
-        <x:v>Combat/DamageScaling.dm</x:v>
+      <x:c r="D6" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Combat/DamageScaling.dm</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -3295,163 +4091,261 @@
     <x:row r="17">
       <x:c r="A17" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Owner resistance penalty</x:t>
+          <x:t xml:space="preserve">Beam skill cooldown</x:t>
         </x:is>
       </x:c>
       <x:c r="B17" s="3">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C17" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">scenario default</x:t>
+          <x:t xml:space="preserve">seconds</x:t>
         </x:is>
       </x:c>
       <x:c r="D17" s="5" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">ProjectileSystem/Projectiles.dm</x:t>
+          <x:t xml:space="preserve">GlobalCombatSettings.dm</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Ki projectile cadence</x:t>
+          <x:t xml:space="preserve">Beam clash winner damage</x:t>
         </x:is>
       </x:c>
       <x:c r="B18" s="3">
-        <x:v>0.5</x:v>
+        <x:v>1.35</x:v>
       </x:c>
       <x:c r="C18" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">deciseconds</x:t>
+          <x:t xml:space="preserve">multiplier</x:t>
         </x:is>
       </x:c>
       <x:c r="D18" s="5" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">ProjectileSystem/Blasts.dm</x:t>
+          <x:t xml:space="preserve">GlobalCombatSettings.dm</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="19">
       <x:c r="A19" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">World FPS</x:t>
+          <x:t xml:space="preserve">Beam clash input pulse</x:t>
         </x:is>
       </x:c>
       <x:c r="B19" s="3">
-        <x:v>60</x:v>
+        <x:v>1.15</x:v>
       </x:c>
       <x:c r="C19" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">frames/second</x:t>
+          <x:t xml:space="preserve">multiplier</x:t>
         </x:is>
       </x:c>
       <x:c r="D19" s="5" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Application/Movement/MovementInput.dm</x:t>
+          <x:t xml:space="preserve">GlobalCombatSettings.dm</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="20">
       <x:c r="A20" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Android incoming damage</x:t>
+          <x:t xml:space="preserve">Owner resistance penalty</x:t>
         </x:is>
       </x:c>
       <x:c r="B20" s="3">
-        <x:v>0.55</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C20" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">multiplier</x:t>
+          <x:t xml:space="preserve">scenario default</x:t>
         </x:is>
       </x:c>
       <x:c r="D20" s="5" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">BackgroundCode/StatLoop.dm</x:t>
+          <x:t xml:space="preserve">ProjectileSystem/Projectiles.dm</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="21">
       <x:c r="A21" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Legendary incoming damage</x:t>
+          <x:t xml:space="preserve">Ki projectile cadence</x:t>
         </x:is>
       </x:c>
       <x:c r="B21" s="3">
-        <x:v>0.9</x:v>
+        <x:v>0.5</x:v>
       </x:c>
       <x:c r="C21" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">multiplier</x:t>
+          <x:t xml:space="preserve">deciseconds</x:t>
         </x:is>
       </x:c>
       <x:c r="D21" s="5" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">BackgroundCode/StatLoop.dm</x:t>
+          <x:t xml:space="preserve">ProjectileSystem/Blasts.dm</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="22">
       <x:c r="A22" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">World FPS</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B22" s="3">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="C22" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">frames/second</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D22" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Application/Movement/MovementInput.dm</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Android incoming damage</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B23" s="3">
+        <x:v>0.55</x:v>
+      </x:c>
+      <x:c r="C23" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">multiplier</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D23" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">BackgroundCode/StatLoop.dm</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Legendary incoming damage</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B24" s="3">
+        <x:v>0.9</x:v>
+      </x:c>
+      <x:c r="C24" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">multiplier</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D24" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">BackgroundCode/StatLoop.dm</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">Jiren incoming damage</x:t>
         </x:is>
       </x:c>
-      <x:c r="B22" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C22" t="inlineStr">
+      <x:c r="B25" s="3">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">multiplier</x:t>
         </x:is>
       </x:c>
-      <x:c r="D22" s="5" t="inlineStr">
+      <x:c r="D25" s="5" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">BackgroundCode/StatLoop.dm</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="23">
-      <x:c r="A23" t="str">
-        <x:v>Beam skill cooldown</x:v>
-      </x:c>
-      <x:c r="B23" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C23" t="str">
-        <x:v>seconds</x:v>
-      </x:c>
-      <x:c r="D23" t="str">
-        <x:v>GlobalCombatSettings.dm</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24">
-      <x:c r="A24" t="str">
-        <x:v>Beam clash winner damage</x:v>
-      </x:c>
-      <x:c r="B24" t="n">
-        <x:v>1.35</x:v>
-      </x:c>
-      <x:c r="C24" t="str">
-        <x:v>multiplier</x:v>
-      </x:c>
-      <x:c r="D24" t="str">
-        <x:v>GlobalCombatSettings.dm</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25">
-      <x:c r="A25" t="str">
-        <x:v>Beam clash input pulse</x:v>
-      </x:c>
-      <x:c r="B25" t="n">
-        <x:v>1.15</x:v>
-      </x:c>
-      <x:c r="C25" t="str">
-        <x:v>multiplier</x:v>
-      </x:c>
-      <x:c r="D25" t="str">
-        <x:v>GlobalCombatSettings.dm</x:v>
+    <x:row r="26">
+      <x:c r="A26" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Standard invested skill target</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B26" s="3">
+        <x:v>12.5</x:v>
+      </x:c>
+      <x:c r="C26" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">5 basic melee hits</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D26" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Balance policy</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">High-commitment skill target</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B27" s="3">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C27" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">8 basic melee hits</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D27" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Balance policy</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Finisher target</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B28" s="3">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C28" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">16 basic melee hits</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D28" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Balance policy</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Kikoho target/self ratio</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B29" s="3">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C29" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">minimum reward-to-risk</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D29" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">GlobalCombatSettings.dm</x:t>
+        </x:is>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -10021,7 +10915,7 @@
         </x:is>
       </x:c>
       <x:c r="E4">
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="F4">
         <x:v>1</x:v>
@@ -10057,7 +10951,7 @@
       </x:c>
       <x:c r="N4" s="5" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Explicit factor; no hidden base multiplier</x:t>
+          <x:t xml:space="preserve">Committed advancing strike</x:t>
         </x:is>
       </x:c>
       <x:c r="O4" s="5" t="inlineStr">
@@ -10087,8 +10981,8 @@
           <x:t xml:space="preserve">Physical</x:t>
         </x:is>
       </x:c>
-      <x:c r="E5" t="n">
-        <x:v>2</x:v>
+      <x:c r="E5">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F5">
         <x:v>5</x:v>
@@ -10120,8 +11014,10 @@
           <x:t xml:space="preserve">None</x:t>
         </x:is>
       </x:c>
-      <x:c r="N5" s="5" t="str">
-        <x:v>Five-hit budget 10; +15 accuracy; knockback only on the finisher</x:v>
+      <x:c r="N5" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Five-hit budget 15; +15 accuracy; knockback only on the finisher</x:t>
+        </x:is>
       </x:c>
       <x:c r="O5" s="5" t="inlineStr">
         <x:is>
@@ -10150,8 +11046,8 @@
           <x:t xml:space="preserve">Physical</x:t>
         </x:is>
       </x:c>
-      <x:c r="E6" t="n">
-        <x:v>0.5</x:v>
+      <x:c r="E6">
+        <x:v>0.75</x:v>
       </x:c>
       <x:c r="F6">
         <x:v>24</x:v>
@@ -10183,8 +11079,10 @@
           <x:t xml:space="preserve">None</x:t>
         </x:is>
       </x:c>
-      <x:c r="N6" s="5" t="str">
-        <x:v>Exactly 24 attempts; budget 12</x:v>
+      <x:c r="N6" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Exactly 24 attempts; budget 18</x:t>
+        </x:is>
       </x:c>
       <x:c r="O6" s="5" t="inlineStr">
         <x:is>
@@ -10213,8 +11111,10 @@
           <x:t xml:space="preserve">Physical</x:t>
         </x:is>
       </x:c>
-      <x:c r="E7" t="str">
-        <x:v>3-12</x:v>
+      <x:c r="E7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">5-18</x:t>
+        </x:is>
       </x:c>
       <x:c r="F7">
         <x:v>1</x:v>
@@ -10246,8 +11146,10 @@
           <x:t xml:space="preserve">None</x:t>
         </x:is>
       </x:c>
-      <x:c r="N7" s="5" t="str">
-        <x:v>Factor scales 0.4 per completed step; no second BP ratio</x:v>
+      <x:c r="N7" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Factor scales 0.55 per completed step; no second BP ratio</x:t>
+        </x:is>
       </x:c>
       <x:c r="O7" s="5" t="inlineStr">
         <x:is>
@@ -10276,8 +11178,8 @@
           <x:t xml:space="preserve">Physical</x:t>
         </x:is>
       </x:c>
-      <x:c r="E8" t="n">
-        <x:v>12</x:v>
+      <x:c r="E8">
+        <x:v>18</x:v>
       </x:c>
       <x:c r="F8">
         <x:v>2</x:v>
@@ -10309,8 +11211,10 @@
           <x:t xml:space="preserve">None</x:t>
         </x:is>
       </x:c>
-      <x:c r="N8" s="5" t="str">
-        <x:v>Two hits: 7 and 5</x:v>
+      <x:c r="N8" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Two hits: 11 and 7</x:t>
+        </x:is>
       </x:c>
       <x:c r="O8" s="5" t="inlineStr">
         <x:is>
@@ -10339,8 +11243,8 @@
           <x:t xml:space="preserve">Physical</x:t>
         </x:is>
       </x:c>
-      <x:c r="E9" t="n">
-        <x:v>10</x:v>
+      <x:c r="E9">
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F9">
         <x:v>1</x:v>
@@ -10354,11 +11258,13 @@
       <x:c r="I9">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J9" t="n">
+      <x:c r="J9">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K9" s="5" t="str">
-        <x:v>1s charge</x:v>
+      <x:c r="K9" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1s charge</x:t>
+        </x:is>
       </x:c>
       <x:c r="L9">
         <x:v>3</x:v>
@@ -10370,7 +11276,7 @@
       </x:c>
       <x:c r="N9" s="5" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">No flat damage; calculated against the victim</x:t>
+          <x:t xml:space="preserve">High-impact charged strike</x:t>
         </x:is>
       </x:c>
       <x:c r="O9" s="5" t="inlineStr">
@@ -10400,8 +11306,8 @@
           <x:t xml:space="preserve">Physical</x:t>
         </x:is>
       </x:c>
-      <x:c r="E10" t="n">
-        <x:v>7.5</x:v>
+      <x:c r="E10">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F10">
         <x:v>1</x:v>
@@ -10418,8 +11324,10 @@
       <x:c r="J10">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="K10" s="5" t="str">
-        <x:v>1s charge</x:v>
+      <x:c r="K10" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1s charge</x:t>
+        </x:is>
       </x:c>
       <x:c r="L10">
         <x:v>3</x:v>
@@ -10431,7 +11339,7 @@
       </x:c>
       <x:c r="N10" s="5" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">No flat damage; calculated against the victim</x:t>
+          <x:t xml:space="preserve">Charged area kick</x:t>
         </x:is>
       </x:c>
       <x:c r="O10" s="5" t="inlineStr">
@@ -10461,8 +11369,8 @@
           <x:t xml:space="preserve">Physical</x:t>
         </x:is>
       </x:c>
-      <x:c r="E11" t="n">
-        <x:v>3.5</x:v>
+      <x:c r="E11">
+        <x:v>8</x:v>
       </x:c>
       <x:c r="F11">
         <x:v>1</x:v>
@@ -10525,7 +11433,7 @@
         </x:is>
       </x:c>
       <x:c r="E12">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F12">
         <x:v>1</x:v>
@@ -10582,14 +11490,18 @@
           <x:t xml:space="preserve">Learnable</x:t>
         </x:is>
       </x:c>
-      <x:c r="D13" t="str">
-        <x:v>Physical</x:v>
-      </x:c>
-      <x:c r="E13" t="n">
-        <x:v>0.55</x:v>
-      </x:c>
-      <x:c r="F13" t="str">
-        <x:v>7-15</x:v>
+      <x:c r="D13" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Physical</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E13">
+        <x:v>0.8</x:v>
+      </x:c>
+      <x:c r="F13" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">7-15</x:t>
+        </x:is>
       </x:c>
       <x:c r="G13">
         <x:v>0</x:v>
@@ -10603,8 +11515,10 @@
       <x:c r="J13">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="K13" s="5" t="str">
-        <x:v>1 tick between rocks</x:v>
+      <x:c r="K13" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1 tick between rocks</x:t>
+        </x:is>
       </x:c>
       <x:c r="L13">
         <x:v>8</x:v>
@@ -10614,8 +11528,10 @@
           <x:t xml:space="preserve">None</x:t>
         </x:is>
       </x:c>
-      <x:c r="N13" s="5" t="str">
-        <x:v>Strength-scaled sequence; maximum shared factor 8.25</x:v>
+      <x:c r="N13" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Strength-scaled sequence; maximum factor 12</x:t>
+        </x:is>
       </x:c>
       <x:c r="O13" s="5" t="inlineStr">
         <x:is>
@@ -10644,8 +11560,8 @@
           <x:t xml:space="preserve">Physical</x:t>
         </x:is>
       </x:c>
-      <x:c r="E14" t="n">
-        <x:v>8</x:v>
+      <x:c r="E14">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F14">
         <x:v>1</x:v>
@@ -10653,8 +11569,10 @@
       <x:c r="G14">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H14" t="str">
-        <x:v>30% mastered splash</x:v>
+      <x:c r="H14" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">30% mastered splash</x:t>
+        </x:is>
       </x:c>
       <x:c r="I14">
         <x:v>100</x:v>
@@ -10707,38 +11625,54 @@
           <x:t xml:space="preserve">Ki</x:t>
         </x:is>
       </x:c>
-      <x:c r="E15" t="str">
-        <x:v>0.105-0.15</x:v>
-      </x:c>
-      <x:c r="F15" t="n">
+      <x:c r="E15" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">0.105-0.15</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F15">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="G15" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H15" t="str">
-        <x:v>Lead only</x:v>
-      </x:c>
-      <x:c r="I15" t="str">
-        <x:v>20% per pellet</x:v>
-      </x:c>
-      <x:c r="J15" t="str">
-        <x:v>Dynamic</x:v>
-      </x:c>
-      <x:c r="K15" s="5" t="str">
-        <x:v>0.75ds base refire</x:v>
-      </x:c>
-      <x:c r="L15" t="n">
+      <x:c r="G15">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H15" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Lead only</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I15" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">20% per pellet</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J15" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Dynamic</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K15" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">0.75ds base refire</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L15">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="M15" s="5" t="str">
-        <x:v>None</x:v>
-      </x:c>
-      <x:c r="N15" s="5" t="str">
-        <x:v>3-pellet fan; shared budget 0.6; lead utility; caps 24/owner and 256/global</x:v>
-      </x:c>
-      <x:c r="O15" s="5" t="str">
-        <x:v>ProjectileSystem/Blasts.dm; SkillEngine.dm</x:v>
+      <x:c r="M15" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">None</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N15" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">3-pellet fan; shared budget 0.6; lead utility; caps 24/owner and 256/global</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O15" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ProjectileSystem/Blasts.dm; SkillEngine.dm</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -10763,7 +11697,7 @@
         </x:is>
       </x:c>
       <x:c r="E16">
-        <x:v>22</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="F16">
         <x:v>2</x:v>
@@ -10773,7 +11707,7 @@
       </x:c>
       <x:c r="H16" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">22 splash</x:t>
+          <x:t xml:space="preserve">28 splash</x:t>
         </x:is>
       </x:c>
       <x:c r="I16">
@@ -10797,7 +11731,7 @@
       </x:c>
       <x:c r="N16" s="5" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">22 direct + 22 splash; budget 44</x:t>
+          <x:t xml:space="preserve">28 direct + 28 splash; budget 56</x:t>
         </x:is>
       </x:c>
       <x:c r="O16" s="5" t="inlineStr">
@@ -10828,7 +11762,7 @@
         </x:is>
       </x:c>
       <x:c r="E17">
-        <x:v>4</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="F17">
         <x:v>2</x:v>
@@ -10838,7 +11772,7 @@
       </x:c>
       <x:c r="H17" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4 splash</x:t>
+          <x:t xml:space="preserve">8 splash</x:t>
         </x:is>
       </x:c>
       <x:c r="I17">
@@ -10862,7 +11796,7 @@
       </x:c>
       <x:c r="N17" s="5" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4 direct + 4 splash</x:t>
+          <x:t xml:space="preserve">8 direct + 8 splash</x:t>
         </x:is>
       </x:c>
       <x:c r="O17" s="5" t="inlineStr">
@@ -10893,7 +11827,7 @@
         </x:is>
       </x:c>
       <x:c r="E18">
-        <x:v>2.5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F18">
         <x:v>2</x:v>
@@ -10903,7 +11837,7 @@
       </x:c>
       <x:c r="H18" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">2.5 splash</x:t>
+          <x:t xml:space="preserve">6 splash</x:t>
         </x:is>
       </x:c>
       <x:c r="I18">
@@ -10927,7 +11861,7 @@
       </x:c>
       <x:c r="N18" s="5" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">2.5 direct + 2.5 splash</x:t>
+          <x:t xml:space="preserve">6 direct + 6 splash</x:t>
         </x:is>
       </x:c>
       <x:c r="O18" s="5" t="inlineStr">
@@ -10957,8 +11891,8 @@
           <x:t xml:space="preserve">Ki</x:t>
         </x:is>
       </x:c>
-      <x:c r="E19" t="n">
-        <x:v>10</x:v>
+      <x:c r="E19">
+        <x:v>18</x:v>
       </x:c>
       <x:c r="F19">
         <x:v>1</x:v>
@@ -10988,8 +11922,10 @@
           <x:t xml:space="preserve">None</x:t>
         </x:is>
       </x:c>
-      <x:c r="N19" s="5" t="str">
-        <x:v>Piercing, guided and owner-immune; 50% decay after each landed pierce</x:v>
+      <x:c r="N19" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Piercing, guided and owner-immune; 50% decay after each landed pierce</x:t>
+        </x:is>
       </x:c>
       <x:c r="O19" s="5" t="inlineStr">
         <x:is>
@@ -11018,8 +11954,8 @@
           <x:t xml:space="preserve">Ki</x:t>
         </x:is>
       </x:c>
-      <x:c r="E20" t="n">
-        <x:v>6</x:v>
+      <x:c r="E20">
+        <x:v>12</x:v>
       </x:c>
       <x:c r="F20">
         <x:v>2</x:v>
@@ -11027,8 +11963,10 @@
       <x:c r="G20">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H20" t="str">
-        <x:v>6 splash</x:v>
+      <x:c r="H20" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">12 splash</x:t>
+        </x:is>
       </x:c>
       <x:c r="I20">
         <x:v>20</x:v>
@@ -11049,8 +11987,10 @@
           <x:t xml:space="preserve">None</x:t>
         </x:is>
       </x:c>
-      <x:c r="N20" s="5" t="str">
-        <x:v>Guided, owner-immune; budget 12</x:v>
+      <x:c r="N20" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Guided, owner-immune; budget 24</x:t>
+        </x:is>
       </x:c>
       <x:c r="O20" s="5" t="inlineStr">
         <x:is>
@@ -11080,7 +12020,7 @@
         </x:is>
       </x:c>
       <x:c r="E21">
-        <x:v>0.5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F21">
         <x:v>4</x:v>
@@ -11114,7 +12054,7 @@
       </x:c>
       <x:c r="N21" s="5" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Four shots</x:t>
+          <x:t xml:space="preserve">Four shots; maximum direct total 8</x:t>
         </x:is>
       </x:c>
       <x:c r="O21" s="5" t="inlineStr">
@@ -11144,8 +12084,8 @@
           <x:t xml:space="preserve">Ki</x:t>
         </x:is>
       </x:c>
-      <x:c r="E22" t="n">
-        <x:v>1</x:v>
+      <x:c r="E22">
+        <x:v>1.5</x:v>
       </x:c>
       <x:c r="F22">
         <x:v>20</x:v>
@@ -11175,8 +12115,10 @@
           <x:t xml:space="preserve">None</x:t>
         </x:is>
       </x:c>
-      <x:c r="N22" s="5" t="str">
-        <x:v>Nondeflectable barrage; shared budget 16 per target</x:v>
+      <x:c r="N22" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Nondeflectable barrage; shared budget 24 per target</x:t>
+        </x:is>
       </x:c>
       <x:c r="O22" s="5" t="inlineStr">
         <x:is>
@@ -11206,7 +12148,7 @@
         </x:is>
       </x:c>
       <x:c r="E23">
-        <x:v>0.3</x:v>
+        <x:v>0.5</x:v>
       </x:c>
       <x:c r="F23" t="inlineStr">
         <x:is>
@@ -11218,7 +12160,7 @@
       </x:c>
       <x:c r="H23" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">0.3 splash</x:t>
+          <x:t xml:space="preserve">0.5 splash</x:t>
         </x:is>
       </x:c>
       <x:c r="I23">
@@ -11242,7 +12184,7 @@
       </x:c>
       <x:c r="N23" s="5" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Shared factor budget 18 per victim</x:t>
+          <x:t xml:space="preserve">Shared factor budget 30 per victim</x:t>
         </x:is>
       </x:c>
       <x:c r="O23" s="5" t="inlineStr">
@@ -11273,7 +12215,7 @@
         </x:is>
       </x:c>
       <x:c r="E24">
-        <x:v>0.25</x:v>
+        <x:v>1.25</x:v>
       </x:c>
       <x:c r="F24">
         <x:v>12</x:v>
@@ -11305,7 +12247,7 @@
       </x:c>
       <x:c r="N24" s="5" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Activation capped at 12</x:t>
+          <x:t xml:space="preserve">Activation capped at 12; maximum total 15</x:t>
         </x:is>
       </x:c>
       <x:c r="O24" s="5" t="inlineStr">
@@ -11336,7 +12278,7 @@
         </x:is>
       </x:c>
       <x:c r="E25">
-        <x:v>0.4</x:v>
+        <x:v>0.75</x:v>
       </x:c>
       <x:c r="F25">
         <x:v>20</x:v>
@@ -11370,7 +12312,7 @@
       </x:c>
       <x:c r="N25" s="5" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">20 shots; shared budget 16</x:t>
+          <x:t xml:space="preserve">20 shots; shared budget 24</x:t>
         </x:is>
       </x:c>
       <x:c r="O25" s="5" t="inlineStr">
@@ -11401,7 +12343,7 @@
         </x:is>
       </x:c>
       <x:c r="E26">
-        <x:v>0.2</x:v>
+        <x:v>0.75</x:v>
       </x:c>
       <x:c r="F26">
         <x:v>20</x:v>
@@ -11433,7 +12375,7 @@
       </x:c>
       <x:c r="N26" s="5" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Activation capped at 20 orbs</x:t>
+          <x:t xml:space="preserve">Activation capped at 20 orbs; maximum total 15</x:t>
         </x:is>
       </x:c>
       <x:c r="O26" s="5" t="inlineStr">
@@ -11480,7 +12422,7 @@
           <x:t xml:space="preserve">Recalculated 500.8</x:t>
         </x:is>
       </x:c>
-      <x:c r="J27" t="n">
+      <x:c r="J27">
         <x:v>3</x:v>
       </x:c>
       <x:c r="K27" s="5" t="inlineStr">
@@ -11496,8 +12438,10 @@
           <x:t xml:space="preserve">None</x:t>
         </x:is>
       </x:c>
-      <x:c r="N27" s="5" t="str">
-        <x:v>Lock ticks uncapped; explosive budget 52; 3s restart cooldown</x:v>
+      <x:c r="N27" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Lock ticks uncapped; explosive budget 52; 3s restart cooldown</x:t>
+        </x:is>
       </x:c>
       <x:c r="O27" s="5" t="inlineStr">
         <x:is>
@@ -11527,7 +12471,7 @@
         </x:is>
       </x:c>
       <x:c r="E28">
-        <x:v>4</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="F28">
         <x:v>1</x:v>
@@ -11543,7 +12487,7 @@
           <x:t xml:space="preserve">Recalculated 27.2</x:t>
         </x:is>
       </x:c>
-      <x:c r="J28" t="n">
+      <x:c r="J28">
         <x:v>3</x:v>
       </x:c>
       <x:c r="K28" s="5" t="inlineStr">
@@ -11559,8 +12503,10 @@
           <x:t xml:space="preserve">None</x:t>
         </x:is>
       </x:c>
-      <x:c r="N28" s="5" t="str">
-        <x:v>Lock ticks uncapped; explosive budget 4; 3s restart cooldown</x:v>
+      <x:c r="N28" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Lock ticks uncapped; explosive budget 12; 3s restart cooldown</x:t>
+        </x:is>
       </x:c>
       <x:c r="O28" s="5" t="inlineStr">
         <x:is>
@@ -11590,7 +12536,7 @@
         </x:is>
       </x:c>
       <x:c r="E29">
-        <x:v>3</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F29">
         <x:v>1</x:v>
@@ -11606,7 +12552,7 @@
           <x:t xml:space="preserve">Recalculated 4.3</x:t>
         </x:is>
       </x:c>
-      <x:c r="J29" t="n">
+      <x:c r="J29">
         <x:v>3</x:v>
       </x:c>
       <x:c r="K29" s="5" t="inlineStr">
@@ -11622,8 +12568,10 @@
           <x:t xml:space="preserve">None</x:t>
         </x:is>
       </x:c>
-      <x:c r="N29" s="5" t="str">
-        <x:v>Lock ticks uncapped; explosive budget 3; 3s restart cooldown</x:v>
+      <x:c r="N29" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Lock ticks uncapped; explosive budget 10; 3s restart cooldown</x:t>
+        </x:is>
       </x:c>
       <x:c r="O29" s="5" t="inlineStr">
         <x:is>
@@ -11653,7 +12601,7 @@
         </x:is>
       </x:c>
       <x:c r="E30">
-        <x:v>3</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="F30">
         <x:v>1</x:v>
@@ -11669,7 +12617,7 @@
           <x:t xml:space="preserve">Recalculated 5</x:t>
         </x:is>
       </x:c>
-      <x:c r="J30" t="n">
+      <x:c r="J30">
         <x:v>3</x:v>
       </x:c>
       <x:c r="K30" s="5" t="inlineStr">
@@ -11685,8 +12633,10 @@
           <x:t xml:space="preserve">None</x:t>
         </x:is>
       </x:c>
-      <x:c r="N30" s="5" t="str">
-        <x:v>Lock ticks uncapped; explosive budget 3; 3s restart cooldown</x:v>
+      <x:c r="N30" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Lock ticks uncapped; explosive budget 12; 3s restart cooldown</x:t>
+        </x:is>
       </x:c>
       <x:c r="O30" s="5" t="inlineStr">
         <x:is>
@@ -11716,7 +12666,7 @@
         </x:is>
       </x:c>
       <x:c r="E31">
-        <x:v>5</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F31">
         <x:v>1</x:v>
@@ -11732,7 +12682,7 @@
           <x:t xml:space="preserve">Recalculated 13.7</x:t>
         </x:is>
       </x:c>
-      <x:c r="J31" t="n">
+      <x:c r="J31">
         <x:v>3</x:v>
       </x:c>
       <x:c r="K31" s="5" t="inlineStr">
@@ -11748,8 +12698,10 @@
           <x:t xml:space="preserve">None</x:t>
         </x:is>
       </x:c>
-      <x:c r="N31" s="5" t="str">
-        <x:v>Lock ticks uncapped; explosive budget 5; shield pierce; 3s cooldown</x:v>
+      <x:c r="N31" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Lock ticks uncapped; explosive budget 16; shield pierce; 3s cooldown</x:t>
+        </x:is>
       </x:c>
       <x:c r="O31" s="5" t="inlineStr">
         <x:is>
@@ -11779,7 +12731,7 @@
         </x:is>
       </x:c>
       <x:c r="E32">
-        <x:v>8</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="F32">
         <x:v>1</x:v>
@@ -11795,7 +12747,7 @@
           <x:t xml:space="preserve">Recalculated 12.9</x:t>
         </x:is>
       </x:c>
-      <x:c r="J32" t="n">
+      <x:c r="J32">
         <x:v>3</x:v>
       </x:c>
       <x:c r="K32" s="5" t="inlineStr">
@@ -11811,8 +12763,10 @@
           <x:t xml:space="preserve">None</x:t>
         </x:is>
       </x:c>
-      <x:c r="N32" s="5" t="str">
-        <x:v>Lock ticks uncapped; explosive budget 8; 3s restart cooldown</x:v>
+      <x:c r="N32" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Lock ticks uncapped; explosive budget 18; 3s restart cooldown</x:t>
+        </x:is>
       </x:c>
       <x:c r="O32" s="5" t="inlineStr">
         <x:is>
@@ -11842,7 +12796,7 @@
         </x:is>
       </x:c>
       <x:c r="E33">
-        <x:v>5</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F33">
         <x:v>1</x:v>
@@ -11858,7 +12812,7 @@
           <x:t xml:space="preserve">Recalculated 8.6</x:t>
         </x:is>
       </x:c>
-      <x:c r="J33" t="n">
+      <x:c r="J33">
         <x:v>3</x:v>
       </x:c>
       <x:c r="K33" s="5" t="inlineStr">
@@ -11874,8 +12828,10 @@
           <x:t xml:space="preserve">None</x:t>
         </x:is>
       </x:c>
-      <x:c r="N33" s="5" t="str">
-        <x:v>Lock ticks uncapped; explosive budget 5; range utility; 3s cooldown</x:v>
+      <x:c r="N33" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Lock ticks uncapped; explosive budget 13; range utility; 3s cooldown</x:t>
+        </x:is>
       </x:c>
       <x:c r="O33" s="5" t="inlineStr">
         <x:is>
@@ -11905,7 +12861,7 @@
         </x:is>
       </x:c>
       <x:c r="E34">
-        <x:v>12</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F34">
         <x:v>1</x:v>
@@ -11921,7 +12877,7 @@
           <x:t xml:space="preserve">Recalculated 21.2</x:t>
         </x:is>
       </x:c>
-      <x:c r="J34" t="n">
+      <x:c r="J34">
         <x:v>3</x:v>
       </x:c>
       <x:c r="K34" s="5" t="inlineStr">
@@ -11937,8 +12893,10 @@
           <x:t xml:space="preserve">None</x:t>
         </x:is>
       </x:c>
-      <x:c r="N34" s="5" t="str">
-        <x:v>Lock ticks uncapped; explosive budget 12; 3s restart cooldown</x:v>
+      <x:c r="N34" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Lock ticks uncapped; explosive budget 24; 3s restart cooldown</x:t>
+        </x:is>
       </x:c>
       <x:c r="O34" s="5" t="inlineStr">
         <x:is>
@@ -11968,7 +12926,7 @@
         </x:is>
       </x:c>
       <x:c r="E35">
-        <x:v>7</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F35">
         <x:v>1</x:v>
@@ -11984,7 +12942,7 @@
           <x:t xml:space="preserve">Recalculated 9</x:t>
         </x:is>
       </x:c>
-      <x:c r="J35" t="n">
+      <x:c r="J35">
         <x:v>3</x:v>
       </x:c>
       <x:c r="K35" s="5" t="inlineStr">
@@ -12000,8 +12958,10 @@
           <x:t xml:space="preserve">None</x:t>
         </x:is>
       </x:c>
-      <x:c r="N35" s="5" t="str">
-        <x:v>Lock ticks uncapped; explosive budget 7; 3s restart cooldown</x:v>
+      <x:c r="N35" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Lock ticks uncapped; explosive budget 17; 3s restart cooldown</x:t>
+        </x:is>
       </x:c>
       <x:c r="O35" s="5" t="inlineStr">
         <x:is>
@@ -12031,7 +12991,7 @@
         </x:is>
       </x:c>
       <x:c r="E36">
-        <x:v>6</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F36">
         <x:v>1</x:v>
@@ -12047,7 +13007,7 @@
           <x:t xml:space="preserve">Recalculated 9.1</x:t>
         </x:is>
       </x:c>
-      <x:c r="J36" t="n">
+      <x:c r="J36">
         <x:v>3</x:v>
       </x:c>
       <x:c r="K36" s="5" t="inlineStr">
@@ -12063,8 +13023,10 @@
           <x:t xml:space="preserve">None</x:t>
         </x:is>
       </x:c>
-      <x:c r="N36" s="5" t="str">
-        <x:v>Lock ticks uncapped; explosive budget 6; range utility; 3s cooldown</x:v>
+      <x:c r="N36" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Lock ticks uncapped; explosive budget 15; range utility; 3s cooldown</x:t>
+        </x:is>
       </x:c>
       <x:c r="O36" s="5" t="inlineStr">
         <x:is>
@@ -12075,51 +13037,49 @@
     <x:row r="37">
       <x:c r="A37" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Explosion</x:t>
+          <x:t xml:space="preserve">Dragon Nova</x:t>
         </x:is>
       </x:c>
       <x:c r="B37" s="5" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">/obj/Attacks/Explosion</x:t>
+          <x:t xml:space="preserve">/obj/Attacks/NexusSpecialStyle/ChargedProjectile/DragonNova</x:t>
         </x:is>
       </x:c>
       <x:c r="C37" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Learnable</x:t>
+          <x:t xml:space="preserve">Test package</x:t>
         </x:is>
       </x:c>
       <x:c r="D37" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Ki AoE</x:t>
+          <x:t xml:space="preserve">Ki</x:t>
         </x:is>
       </x:c>
       <x:c r="E37">
-        <x:v>3</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="F37">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="G37">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H37">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="I37">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="J37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2*SD(.35)</x:t>
-        </x:is>
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="J37">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K37" s="5" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">No charge</x:t>
+          <x:t xml:space="preserve">2.4s charge</x:t>
         </x:is>
       </x:c>
       <x:c r="L37">
-        <x:v>20</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="M37" s="5" t="inlineStr">
         <x:is>
@@ -12128,63 +13088,61 @@
       </x:c>
       <x:c r="N37" s="5" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Force versus Resistance</x:t>
+          <x:t xml:space="preserve">Direct plus equal splash; budget cap 36</x:t>
         </x:is>
       </x:c>
       <x:c r="O37" s="5" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SkillEngine.dm</x:t>
+          <x:t xml:space="preserve">Combat/NexusSpecialStyles.dm</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="38">
       <x:c r="A38" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Shockwave</x:t>
+          <x:t xml:space="preserve">Sky Break</x:t>
         </x:is>
       </x:c>
       <x:c r="B38" s="5" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">/obj/Attacks/Shockwave</x:t>
+          <x:t xml:space="preserve">/obj/Attacks/NexusSpecialStyle/ChargedProjectile/SkyBreak</x:t>
         </x:is>
       </x:c>
       <x:c r="C38" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Learnable</x:t>
+          <x:t xml:space="preserve">Test package</x:t>
         </x:is>
       </x:c>
       <x:c r="D38" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Hybrid AoE</x:t>
+          <x:t xml:space="preserve">Physical</x:t>
         </x:is>
       </x:c>
       <x:c r="E38">
-        <x:v>0.5</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F38">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="G38">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H38">
-        <x:v>10</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="I38">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="J38" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">7*SD(.25)</x:t>
-        </x:is>
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="J38">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="K38" s="5" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">No charge</x:t>
+          <x:t xml:space="preserve">1.6s charge</x:t>
         </x:is>
       </x:c>
       <x:c r="L38">
-        <x:v>10</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="M38" s="5" t="inlineStr">
         <x:is>
@@ -12193,38 +13151,38 @@
       </x:c>
       <x:c r="N38" s="5" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Half physical and half Ki per pulse</x:t>
+          <x:t xml:space="preserve">Strength-scaled direct plus splash; weapon required; budget cap 26</x:t>
         </x:is>
       </x:c>
       <x:c r="O38" s="5" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SkillEngine.dm</x:t>
+          <x:t xml:space="preserve">Combat/NexusSpecialStyles.dm</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="39">
       <x:c r="A39" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Kikoho</x:t>
+          <x:t xml:space="preserve">Echoing Slash</x:t>
         </x:is>
       </x:c>
       <x:c r="B39" s="5" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">/obj/Attacks/Kikoho</x:t>
+          <x:t xml:space="preserve">/obj/Attacks/NexusSpecialStyle/ChargedProjectile/EchoingSlash</x:t>
         </x:is>
       </x:c>
       <x:c r="C39" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Granted</x:t>
+          <x:t xml:space="preserve">Test package</x:t>
         </x:is>
       </x:c>
       <x:c r="D39" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Ki</x:t>
+          <x:t xml:space="preserve">Physical</x:t>
         </x:is>
       </x:c>
       <x:c r="E39">
-        <x:v>7</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F39">
         <x:v>1</x:v>
@@ -12236,18 +13194,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I39">
-        <x:v>100</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="J39">
-        <x:v>0</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="K39" s="5" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">0.5*(5+11*SD(.4))</x:t>
+          <x:t xml:space="preserve">0.8s charge</x:t>
         </x:is>
       </x:c>
       <x:c r="L39">
-        <x:v>11</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="M39" s="5" t="inlineStr">
         <x:is>
@@ -12256,43 +13214,41 @@
       </x:c>
       <x:c r="N39" s="5" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Instant hit; separate self-damage pool +24</x:t>
+          <x:t xml:space="preserve">Strength-scaled cutting wave; weapon required; no explosion</x:t>
         </x:is>
       </x:c>
       <x:c r="O39" s="5" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Combat/KiSkills/Kikoho2016.dm</x:t>
+          <x:t xml:space="preserve">Combat/NexusSpecialStyles.dm</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="40">
       <x:c r="A40" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Omega Bomb</x:t>
+          <x:t xml:space="preserve">Explosion</x:t>
         </x:is>
       </x:c>
       <x:c r="B40" s="5" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">/obj/Attacks/Genki_Dama</x:t>
+          <x:t xml:space="preserve">/obj/Attacks/Explosion</x:t>
         </x:is>
       </x:c>
       <x:c r="C40" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Granted</x:t>
+          <x:t xml:space="preserve">Learnable</x:t>
         </x:is>
       </x:c>
       <x:c r="D40" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Ki charge</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E40" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">4-15</x:t>
-        </x:is>
+          <x:t xml:space="preserve">Ki AoE</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E40">
+        <x:v>12</x:v>
       </x:c>
       <x:c r="F40">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G40">
         <x:v>0</x:v>
@@ -12301,18 +13257,20 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I40">
-        <x:v>1000</x:v>
-      </x:c>
-      <x:c r="J40">
-        <x:v>90</x:v>
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="J40" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2*SD(.35)</x:t>
+        </x:is>
       </x:c>
       <x:c r="K40" s="5" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">25-100% charge</x:t>
+          <x:t xml:space="preserve">No charge</x:t>
         </x:is>
       </x:c>
       <x:c r="L40">
-        <x:v>100</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="M40" s="5" t="inlineStr">
         <x:is>
@@ -12321,63 +13279,63 @@
       </x:c>
       <x:c r="N40" s="5" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Equal direct+splash; total 8-30</x:t>
+          <x:t xml:space="preserve">Force versus Resistance</x:t>
         </x:is>
       </x:c>
       <x:c r="O40" s="5" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Combat/KiSkills/SpiritBomb2016.dm</x:t>
+          <x:t xml:space="preserve">SkillEngine.dm</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="41">
       <x:c r="A41" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Death Ball</x:t>
+          <x:t xml:space="preserve">Shockwave</x:t>
         </x:is>
       </x:c>
       <x:c r="B41" s="5" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">/obj/Attacks/Genki_Dama/Death_Ball</x:t>
+          <x:t xml:space="preserve">/obj/Attacks/Shockwave</x:t>
         </x:is>
       </x:c>
       <x:c r="C41" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Learnable/granted</x:t>
+          <x:t xml:space="preserve">Learnable</x:t>
         </x:is>
       </x:c>
       <x:c r="D41" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Ki charge</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E41" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2.5-10</x:t>
-        </x:is>
+          <x:t xml:space="preserve">Hybrid AoE</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E41">
+        <x:v>1.5</x:v>
       </x:c>
       <x:c r="F41">
-        <x:v>1</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="G41">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H41">
-        <x:v>0</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="I41">
-        <x:v>750</x:v>
-      </x:c>
-      <x:c r="J41">
-        <x:v>0</x:v>
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="J41" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">7*SD(.25)</x:t>
+        </x:is>
       </x:c>
       <x:c r="K41" s="5" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">25-100% charge</x:t>
+          <x:t xml:space="preserve">No charge</x:t>
         </x:is>
       </x:c>
       <x:c r="L41">
-        <x:v>100</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="M41" s="5" t="inlineStr">
         <x:is>
@@ -12386,63 +13344,61 @@
       </x:c>
       <x:c r="N41" s="5" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Explicit capped interpolation</x:t>
+          <x:t xml:space="preserve">Seven pulses; maximum per-target budget 10.5</x:t>
         </x:is>
       </x:c>
       <x:c r="O41" s="5" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Combat/KiSkills/DeathBall2017.dm</x:t>
+          <x:t xml:space="preserve">SkillEngine.dm</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="42">
       <x:c r="A42" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Supernova</x:t>
+          <x:t xml:space="preserve">Kikoho</x:t>
         </x:is>
       </x:c>
       <x:c r="B42" s="5" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">/obj/Attacks/Genki_Dama/Supernova</x:t>
+          <x:t xml:space="preserve">/obj/Attacks/Kikoho</x:t>
         </x:is>
       </x:c>
       <x:c r="C42" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Learnable/granted</x:t>
+          <x:t xml:space="preserve">Granted</x:t>
         </x:is>
       </x:c>
       <x:c r="D42" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Ki charge</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E42" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2-5</x:t>
-        </x:is>
+          <x:t xml:space="preserve">Ki</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E42">
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F42">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G42">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H42">
-        <x:v>5</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I42">
-        <x:v>500</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="J42">
         <x:v>0</x:v>
       </x:c>
       <x:c r="K42" s="5" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">25-100% charge</x:t>
+          <x:t xml:space="preserve">0.5*(5+11*SD(.4))</x:t>
         </x:is>
       </x:c>
       <x:c r="L42">
-        <x:v>100</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="M42" s="5" t="inlineStr">
         <x:is>
@@ -12451,67 +13407,63 @@
       </x:c>
       <x:c r="N42" s="5" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Equal direct+splash; total 4-10</x:t>
+          <x:t xml:space="preserve">Instant hit; separate self-damage pool +6%</x:t>
         </x:is>
       </x:c>
       <x:c r="O42" s="5" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Combat/KiSkills/Supernova.dm</x:t>
+          <x:t xml:space="preserve">Combat/KiSkills/Kikoho2016.dm</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="43">
       <x:c r="A43" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Final Explosion</x:t>
+          <x:t xml:space="preserve">Omega Bomb</x:t>
         </x:is>
       </x:c>
       <x:c r="B43" s="5" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">/obj/Final_Explosion</x:t>
+          <x:t xml:space="preserve">/obj/Attacks/Genki_Dama</x:t>
         </x:is>
       </x:c>
       <x:c r="C43" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Learnable</x:t>
+          <x:t xml:space="preserve">Granted</x:t>
         </x:is>
       </x:c>
       <x:c r="D43" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Ki AoE</x:t>
+          <x:t xml:space="preserve">Ki charge</x:t>
         </x:is>
       </x:c>
       <x:c r="E43" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1-5</x:t>
+          <x:t xml:space="preserve">8-30</x:t>
         </x:is>
       </x:c>
       <x:c r="F43">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G43">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H43">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G43">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H43" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Charge-scaled radius</x:t>
-        </x:is>
-      </x:c>
       <x:c r="I43">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="J43">
-        <x:v>0</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="K43" s="5" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Total 5-25</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="L43" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Dynamic</x:t>
-        </x:is>
+          <x:t xml:space="preserve">25-100% charge</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L43">
+        <x:v>100</x:v>
       </x:c>
       <x:c r="M43" s="5" t="inlineStr">
         <x:is>
@@ -12520,24 +13472,24 @@
       </x:c>
       <x:c r="N43" s="5" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Five stacks; visual range decoupled from damage</x:t>
+          <x:t xml:space="preserve">Equal direct+splash; total 16-60</x:t>
         </x:is>
       </x:c>
       <x:c r="O43" s="5" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Combat/KiSkills/FinalExplosion.dm</x:t>
+          <x:t xml:space="preserve">Combat/KiSkills/SpiritBomb2016.dm</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="44">
       <x:c r="A44" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Self Destruct</x:t>
+          <x:t xml:space="preserve">Death Ball</x:t>
         </x:is>
       </x:c>
       <x:c r="B44" s="5" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">/obj/Self_Destruct</x:t>
+          <x:t xml:space="preserve">/obj/Attacks/Genki_Dama/Death_Ball</x:t>
         </x:is>
       </x:c>
       <x:c r="C44" t="inlineStr">
@@ -12547,11 +13499,13 @@
       </x:c>
       <x:c r="D44" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Ki AoE</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E44">
-        <x:v>30</x:v>
+          <x:t xml:space="preserve">Ki charge</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E44" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">8-28</x:t>
+        </x:is>
       </x:c>
       <x:c r="F44">
         <x:v>1</x:v>
@@ -12560,23 +13514,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H44">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="I44" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Caster dies</x:t>
-        </x:is>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I44">
+        <x:v>750</x:v>
       </x:c>
       <x:c r="J44">
-        <x:v>1200</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K44" s="5" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">No charge</x:t>
+          <x:t xml:space="preserve">25-100% charge</x:t>
         </x:is>
       </x:c>
       <x:c r="L44">
-        <x:v>10</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="M44" s="5" t="inlineStr">
         <x:is>
@@ -12585,63 +13537,63 @@
       </x:c>
       <x:c r="N44" s="5" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Rebuild/Regenerate x0.5; no repeated anger hit</x:t>
+          <x:t xml:space="preserve">Explicit capped interpolation</x:t>
         </x:is>
       </x:c>
       <x:c r="O44" s="5" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Combat/Skills.dm</x:t>
+          <x:t xml:space="preserve">Combat/KiSkills/DeathBall2017.dm</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="45">
       <x:c r="A45" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Hakai</x:t>
+          <x:t xml:space="preserve">Supernova</x:t>
         </x:is>
       </x:c>
       <x:c r="B45" s="5" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">/obj/Hakai</x:t>
+          <x:t xml:space="preserve">/obj/Attacks/Genki_Dama/Supernova</x:t>
         </x:is>
       </x:c>
       <x:c r="C45" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Granted</x:t>
+          <x:t xml:space="preserve">Learnable/granted</x:t>
         </x:is>
       </x:c>
       <x:c r="D45" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Execution</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E45">
-        <x:v>0</x:v>
+          <x:t xml:space="preserve">Ki charge</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E45" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">6-18</x:t>
+        </x:is>
       </x:c>
       <x:c r="F45">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="G45">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H45">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I45" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">25% current Ki</x:t>
-        </x:is>
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="I45">
+        <x:v>500</x:v>
       </x:c>
       <x:c r="J45">
-        <x:v>30</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K45" s="5" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">About 8.5s</x:t>
+          <x:t xml:space="preserve">25-100% charge</x:t>
         </x:is>
       </x:c>
       <x:c r="L45">
-        <x:v>20</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="M45" s="5" t="inlineStr">
         <x:is>
@@ -12650,223 +13602,2748 @@
       </x:c>
       <x:c r="N45" s="5" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Requires BP &gt;=2.2x target; still forced death</x:t>
+          <x:t xml:space="preserve">Equal direct+splash; total 12-36</x:t>
         </x:is>
       </x:c>
       <x:c r="O45" s="5" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Combat/KiSkills/Hakai.dm</x:t>
+          <x:t xml:space="preserve">Combat/KiSkills/Supernova.dm</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="46">
       <x:c r="A46" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">Final Explosion</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B46" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">/obj/Final_Explosion</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C46" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Learnable</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D46" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Ki AoE</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E46" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2-8</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F46">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G46">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H46" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Charge-scaled radius</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I46">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J46">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K46" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Total 10-40</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L46" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Dynamic</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M46" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">None</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N46" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Five stacks; visual range decoupled from damage</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O46" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Combat/KiSkills/FinalExplosion.dm</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Self Destruct</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B47" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">/obj/Self_Destruct</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C47" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Learnable/granted</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D47" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Ki AoE</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E47">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="F47">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G47">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H47">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="I47" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Caster dies</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J47">
+        <x:v>1200</x:v>
+      </x:c>
+      <x:c r="K47" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">No charge</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L47">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="M47" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">None</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N47" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Rebuild/Regenerate x0.5; no repeated anger hit</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O47" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Combat/Skills.dm</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Hakai</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B48" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">/obj/Hakai</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C48" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Granted</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D48" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Execution</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E48">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F48">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G48">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H48">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I48" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">25% current Ki</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J48">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="K48" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">About 8.5s</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L48">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="M48" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">None</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N48" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Requires BP &gt;=2.2x target; still forced death</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O48" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Combat/KiSkills/Hakai.dm</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">Planet Destroy</x:t>
         </x:is>
       </x:c>
-      <x:c r="B46" s="5" t="inlineStr">
+      <x:c r="B49" s="5" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">/obj/Planet_Destroy</x:t>
         </x:is>
       </x:c>
-      <x:c r="C46" t="inlineStr">
+      <x:c r="C49" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Learnable/granted</x:t>
         </x:is>
       </x:c>
-      <x:c r="D46" t="inlineStr">
+      <x:c r="D49" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">World Ki hazard</x:t>
         </x:is>
       </x:c>
-      <x:c r="E46">
+      <x:c r="E49">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F49">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G49">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H49" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Radius 2 events</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I49">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J49" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Planet 21600</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K49" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">70*SD(.3)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L49" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Planet</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M49" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">None</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N49" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Shared per-victim hazard budget 30</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O49" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">WorldMechanics/PlanetDestroy.dm</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="50">
+      <x:c r="A50" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Nexus Beam</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B50" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">/obj/Attacks/RoleplayBeam</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C50" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Ported progression</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D50" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Ki Beam</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E50">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F50">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G50">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="H50">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I50">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="J50">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K50" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Beam toggle</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L50">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="M50" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">None</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N50" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Baseline integrated beam</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O50" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ProjectileSystem/NexusBeams.dm</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="51">
+      <x:c r="A51" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Double Sunday</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B51" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">/obj/Attacks/RoleplayBeam/DoubleSunday</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C51" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Ported progression</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D51" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Ki Beam</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E51">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F51">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G51">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="H51">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I51">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="J51">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K51" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Beam toggle</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L51">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="M51" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">None</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N51" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Wide balanced beam</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O51" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ProjectileSystem/NexusBeams.dm</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="52">
+      <x:c r="A52" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Photon Flash</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B52" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">/obj/Attacks/RoleplayBeam/PhotonFlash</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C52" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Ported progression</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D52" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Ki Beam</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E52">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F52">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G52">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H52">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I52">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="J52">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K52" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Beam toggle</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L52">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="M52" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">None</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N52" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Fast control beam</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O52" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ProjectileSystem/NexusBeams.dm</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="53">
+      <x:c r="A53" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Tyrant Lancer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B53" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">/obj/Attacks/RoleplayBeam/TyrantLancer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C53" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Ported progression</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D53" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Ki Beam</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E53">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F53">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G53">
+        <x:v>1.2</x:v>
+      </x:c>
+      <x:c r="H53">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I53">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="J53">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K53" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Beam toggle</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L53">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="M53" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">None</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N53" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Shield pierce 1.8x; gains power with range</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O53" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ProjectileSystem/NexusBeams.dm</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="54">
+      <x:c r="A54" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Buster Cannon</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B54" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">/obj/Attacks/RoleplayBeam/BusterCannon</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C54" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Ported progression</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D54" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Ki Beam</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E54">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="F54">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G54">
+        <x:v>1.8</x:v>
+      </x:c>
+      <x:c r="H54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I54">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="J54">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K54" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Beam toggle</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L54">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="M54" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">None</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N54" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Slow raw-impact beam</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O54" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ProjectileSystem/NexusBeams.dm</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="55">
+      <x:c r="A55" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Wall of Flame</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B55" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">/obj/Attacks/NexusSpecialStyle/WallOfFlame</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C55" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Ported progression</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D55" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Ki field</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E55">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F46">
+      <x:c r="F55">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G55">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H55">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I55">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="J55">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="K55" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Persistent pulses</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L55">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="M55" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">None</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N55" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Maximum per-target total 12</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O55" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Combat/NexusSpecialStyles.dm</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="56">
+      <x:c r="A56" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Super Explosive Wave</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B56" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">/obj/Attacks/NexusAreaTechnique/SuperExplosiveWave</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C56" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Ported progression</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D56" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Ki AoE</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E56">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="F56">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G56">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H56">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="I56">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="J56">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="K56" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Instant area</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L56">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="M56" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">None</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N56" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Intercepts hostile non-beam blasts</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O56" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Combat/NexusSpecialStyles.dm</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="57">
+      <x:c r="A57" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Earthquake</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B57" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">/obj/Attacks/NexusAreaTechnique/Earthquake</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C57" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Ported progression</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D57" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Physical AoE</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E57">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="G46">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H46" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Radius 2 events</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I46">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J46" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Planet 21600</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K46" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">70*SD(.3)</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="L46" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Planet</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="M46" s="5" t="inlineStr">
+      <x:c r="F57">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G57">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H57">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I57">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="J57">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="K57" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Instant area</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L57">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="M57" s="5" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">None</x:t>
         </x:is>
       </x:c>
-      <x:c r="N46" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Shared per-victim hazard budget 20</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O46" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">WorldMechanics/PlanetDestroy.dm</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="47">
-      <x:c r="A47" t="str">
-        <x:v>Dragon Nova</x:v>
-      </x:c>
-      <x:c r="B47" t="str">
-        <x:v>/obj/Attacks/TenkaichiSpecialStyle/ChargedProjectile/DragonNova</x:v>
-      </x:c>
-      <x:c r="C47" t="str">
-        <x:v>Test package</x:v>
-      </x:c>
-      <x:c r="D47" t="str">
-        <x:v>Ki</x:v>
-      </x:c>
-      <x:c r="E47" t="n">
+      <x:c r="N57" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Ground-only pull; distance falloff</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O57" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Combat/NexusSpecialStyles.dm</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="58">
+      <x:c r="A58" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Super Ghost Kamikaze</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B58" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">/obj/Attacks/NexusSpecialStyle/SuperGhostKamikaze</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C58" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Ported progression</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D58" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Ki</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E58">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="F58">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G58">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H58">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I58">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="J58">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="K58" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Three homing ghosts</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L58">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="M58" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">None</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N58" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Shared per-target budget 18</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O58" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Combat/NexusSpecialStyles.dm</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="59">
+      <x:c r="A59" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Fireball</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B59" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">/obj/ArcaneSpell/Projectile/Fireball</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C59" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Magic progression</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D59" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Ki</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E59">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="F59">
+        <x:v>1.7</x:v>
+      </x:c>
+      <x:c r="G59">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H59" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">70% splash</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I59" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">18 essence</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J59">
+        <x:v>2.4</x:v>
+      </x:c>
+      <x:c r="K59" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Instant projectile</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L59">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="M59" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">None</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N59" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Maximum direct+splash factor 13.6</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O59" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Technology/NexusMagic.dm</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="60">
+      <x:c r="A60" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Frost Bolt</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B60" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">/obj/ArcaneSpell/Projectile/FrostBolt</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C60" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Magic progression</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D60" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Ki</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E60">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="F60">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G60">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H60">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I60" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">15 essence</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J60">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K60" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Instant projectile</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L60">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="M60" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">None</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N60" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Brief stun</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O60" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Technology/NexusMagic.dm</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="61">
+      <x:c r="A61" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Lightning Bolt</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B61" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">/obj/ArcaneSpell/Projectile/LightningBolt</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C61" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Magic progression</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D61" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Ki</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E61">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F61">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G61">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H61">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I61" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">20 essence</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J61">
+        <x:v>3.2</x:v>
+      </x:c>
+      <x:c r="K61" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Instant projectile</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L61">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="M61" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">None</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N61" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Fast stunning projectile</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O61" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Technology/NexusMagic.dm</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="62">
+      <x:c r="A62" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Frost Nova</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B62" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">/obj/ArcaneSpell/FrostNova</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C62" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Magic progression</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D62" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Ki AoE</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E62">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="F47" t="n">
+      <x:c r="F62">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G62">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H62">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I62" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">35 essence</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J62">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="K62" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Instant area</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L62">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="G47" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H47" t="n">
+      <x:c r="M62" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">None</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N62" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Damages and stuns every valid nearby target</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O62" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Technology/NexusMagic.dm</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="63">
+      <x:c r="A63" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Slice</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B63" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">/obj/Attacks/NexusMeleeTechnique/Slice</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C63" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Weapon progression</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D63" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Physical melee</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E63">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="F63">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G63">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H63">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I63">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="I47" t="n">
-        <x:v>200</x:v>
-      </x:c>
-      <x:c r="J47" t="n">
+      <x:c r="J63">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="K63" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Immediate</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L63">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M63" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Weapon</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N63" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Fast baseline weapon skill</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O63" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Combat/NexusMeleeTechniques.dm</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="64">
+      <x:c r="A64" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Bash</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B64" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">/obj/Attacks/NexusMeleeTechnique/Bash</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C64" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Weapon progression</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D64" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Physical melee</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E64">
+        <x:v>2.5</x:v>
+      </x:c>
+      <x:c r="F64">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G64">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H64">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I64">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="J64">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="K64" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Immediate</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L64">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M64" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Weapon</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N64" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Stun utility</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O64" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Combat/NexusMeleeTechniques.dm</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="65">
+      <x:c r="A65" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Flourish</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B65" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">/obj/Attacks/NexusMeleeTechnique/Flourish</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C65" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Weapon progression</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D65" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Physical melee</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E65">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F65">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G65">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H65">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I65">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="J65">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K65" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Immediate</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L65">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M65" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Weapon</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N65" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">High-accuracy impact</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O65" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Combat/NexusMeleeTechniques.dm</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="66">
+      <x:c r="A66" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Wind Howl</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B66" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">/obj/Attacks/NexusMeleeTechnique/WindHowl</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C66" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Weapon progression</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D66" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Physical AoE</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E66">
+        <x:v>2.5</x:v>
+      </x:c>
+      <x:c r="F66">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G66">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H66">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I66">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="J66">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="K47" t="str">
-        <x:v>2.4s charge</x:v>
-      </x:c>
-      <x:c r="L47" t="n">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="M47" t="str">
-        <x:v>None</x:v>
-      </x:c>
-      <x:c r="N47" t="str">
-        <x:v>Direct plus equal splash; budget cap 24</x:v>
-      </x:c>
-      <x:c r="O47" t="str">
-        <x:v>Combat/TenkaichiSpecialStyles.dm</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="48">
-      <x:c r="A48" t="str">
-        <x:v>Sky Break</x:v>
-      </x:c>
-      <x:c r="B48" t="str">
-        <x:v>/obj/Attacks/TenkaichiSpecialStyle/ChargedProjectile/SkyBreak</x:v>
-      </x:c>
-      <x:c r="C48" t="str">
-        <x:v>Test package</x:v>
-      </x:c>
-      <x:c r="D48" t="str">
-        <x:v>Physical</x:v>
-      </x:c>
-      <x:c r="E48" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="F48" t="n">
+      <x:c r="K66" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Instant radial</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L66">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M66" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Weapon</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N66" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">75% splash against up to 12 targets</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O66" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Combat/NexusMeleeTechniques.dm</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="67">
+      <x:c r="A67" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Iai Slash</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B67" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">/obj/Attacks/NexusMeleeTechnique/IaiSlash</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C67" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Weapon progression</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D67" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Physical melee</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E67">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F67">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G67">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H67">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I67">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J67">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K67" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Dash strike</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L67">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="M67" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Weapon</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N67" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Pass-through line attack</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O67" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Combat/NexusMeleeTechniques.dm</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="68">
+      <x:c r="A68" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Riposte</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B68" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">/obj/Attacks/NexusMeleeTechnique/Riposte</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C68" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Weapon progression</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D68" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Physical melee</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E68">
+        <x:v>4.5</x:v>
+      </x:c>
+      <x:c r="F68">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G68">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H68">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I68">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="J68">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K68" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Counter window</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L68">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M68" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Weapon</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N68" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Guaranteed counter accuracy</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O68" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Combat/NexusMeleeTechniques.dm</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="69">
+      <x:c r="A69" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Cleave</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B69" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">/obj/Attacks/NexusMeleeTechnique/Cleave</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C69" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Weapon progression</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D69" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Physical AoE</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E69">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F69">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G69">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H69">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I69">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="J69">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="K69" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Front sweep</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L69">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M69" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Weapon</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N69" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">65% splash against two targets</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O69" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Combat/NexusMeleeTechniques.dm</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="70">
+      <x:c r="A70" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Sword Stab</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B70" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">/obj/Attacks/NexusMeleeTechnique/SwordStab</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C70" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Weapon progression</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D70" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Physical melee</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E70">
+        <x:v>4.5</x:v>
+      </x:c>
+      <x:c r="F70">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G70">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H70">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I70">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="J70">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K70" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Immediate</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L70">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="G48" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H48" t="n">
+      <x:c r="M70" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Weapon</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N70" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Line pierce and bleed</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O70" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Combat/NexusMeleeTechniques.dm</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="71">
+      <x:c r="A71" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Overhead Smash</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B71" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">/obj/Attacks/NexusMeleeTechnique/OverheadSmash</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C71" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Weapon progression</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D71" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Physical melee</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E71">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F71">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G71">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H71">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I71">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J71">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K71" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Immediate</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L71">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M71" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Weapon</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N71" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Lower accuracy; line impact</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O71" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Combat/NexusMeleeTechniques.dm</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="72">
+      <x:c r="A72" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Colossal Impact</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B72" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">/obj/Attacks/NexusMeleeTechnique/ColossalImpact</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C72" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Weapon progression</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D72" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Physical AoE</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E72">
+        <x:v>3.5</x:v>
+      </x:c>
+      <x:c r="F72">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G72">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H72">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I72">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="J72">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="K72" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Instant radial</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L72">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="I48" t="n">
-        <x:v>180</x:v>
-      </x:c>
-      <x:c r="J48" t="n">
+      <x:c r="M72" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Weapon</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N72" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">65% splash against up to 12 targets</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O72" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Combat/NexusMeleeTechniques.dm</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="73">
+      <x:c r="A73" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Burning Slash</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B73" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">/obj/Attacks/NexusMeleeTechnique/BurningSlash</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C73" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Weapon progression</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D73" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Physical melee</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E73">
+        <x:v>1.8</x:v>
+      </x:c>
+      <x:c r="F73">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G73">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H73">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I73">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="J73">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="K73" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Three-hit combo</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L73">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M73" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Weapon</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N73" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Weighted total 3.96 plus bleed</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O73" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Combat/NexusMeleeTechniques.dm</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="74">
+      <x:c r="A74" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Headbutt</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B74" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">/obj/Attacks/NexusMeleeTechnique/Headbutt</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C74" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Unarmed progression</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D74" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Physical melee</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E74">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F74">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G74">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H74">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I74">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="J74">
+        <x:v>5.5</x:v>
+      </x:c>
+      <x:c r="K74" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Immediate</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L74">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M74" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Unarmed</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N74" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Brief stagger</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O74" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Combat/NexusMeleeTechniques.dm</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="75">
+      <x:c r="A75" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Uppercut Combo</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B75" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">/obj/Attacks/NexusMeleeTechnique/UppercutCombo</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C75" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Unarmed progression</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D75" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Physical melee</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E75">
+        <x:v>2.2</x:v>
+      </x:c>
+      <x:c r="F75">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G75">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H75">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I75">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="J75">
+        <x:v>7.5</x:v>
+      </x:c>
+      <x:c r="K75" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Three-hit combo</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L75">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M75" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Unarmed</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N75" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Weighted total 5.5; finisher launch</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O75" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Combat/NexusMeleeTechniques.dm</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="76">
+      <x:c r="A76" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Axe Kick</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B76" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">/obj/Attacks/NexusMeleeTechnique/AxeKick</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C76" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Unarmed progression</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D76" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Physical melee</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E76">
+        <x:v>4.5</x:v>
+      </x:c>
+      <x:c r="F76">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G76">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H76">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I76">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="J76">
+        <x:v>6.5</x:v>
+      </x:c>
+      <x:c r="K76" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Immediate</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L76">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M76" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Unarmed</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N76" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Strong knockback</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O76" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Combat/NexusMeleeTechniques.dm</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="77">
+      <x:c r="A77" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Kickback Combo</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B77" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">/obj/Attacks/NexusMeleeTechnique/KickbackCombo</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C77" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Unarmed progression</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D77" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Physical melee</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E77">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F77">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G77">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H77">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I77">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="J77">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="K77" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Pursuit combo</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L77">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M77" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Unarmed</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N77" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Weighted total 5.4</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O77" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Combat/NexusMeleeTechniques.dm</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="78">
+      <x:c r="A78" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">March of Fury</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B78" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">/obj/Attacks/NexusMeleeTechnique/MarchOfFury</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C78" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Unarmed progression</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D78" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Physical melee</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E78">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F78">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G78">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H78">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I78">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="J78">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K78" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Advancing sequence</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L78">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M78" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Unarmed</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N78" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Weighted total 7.2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O78" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Combat/NexusMeleeTechniques.dm</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="79">
+      <x:c r="A79" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Pile Driver</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B79" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">/obj/Attacks/NexusMeleeTechnique/PileDriver</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C79" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Unarmed progression</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D79" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Physical melee</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E79">
+        <x:v>5.5</x:v>
+      </x:c>
+      <x:c r="F79">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G79">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H79">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I79">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="J79">
+        <x:v>12.5</x:v>
+      </x:c>
+      <x:c r="K79" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Grab slam</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L79">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M79" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Grabbed target</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N79" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Unavoidable impact</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O79" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Combat/NexusMeleeTechniques.dm</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="80">
+      <x:c r="A80" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Megaton Throw</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B80" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">/obj/Attacks/NexusMeleeTechnique/MegatonThrow</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C80" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Unarmed progression</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D80" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Physical melee</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E80">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F80">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G80">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H80">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I80">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J80">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="K80" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Grab throw</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L80">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M80" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Grabbed target</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N80" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Throw finisher</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O80" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Combat/NexusMeleeTechniques.dm</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="81">
+      <x:c r="A81" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Consecutive Normal Punches</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B81" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">/obj/Attacks/NexusMeleeTechnique/ConsecutiveNormalPunches</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C81" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Unarmed progression</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D81" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Physical melee</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E81">
+        <x:v>2.3</x:v>
+      </x:c>
+      <x:c r="F81">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G81">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H81">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I81">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="J81">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K81" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Delayed barrage</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L81">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M81" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Unarmed</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N81" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Weighted total 6.9</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O81" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Combat/NexusMeleeTechniques.dm</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="82">
+      <x:c r="A82" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Exploding Heart Strike</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B82" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">/obj/Attacks/NexusMeleeTechnique/ExplodingHeartStrike</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C82" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Unarmed progression</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D82" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Physical melee</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E82">
+        <x:v>4.5</x:v>
+      </x:c>
+      <x:c r="F82">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G82">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H82">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I82">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="J82">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="K48" t="str">
-        <x:v>1.6s charge</x:v>
-      </x:c>
-      <x:c r="L48" t="n">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="M48" t="str">
-        <x:v>None</x:v>
-      </x:c>
-      <x:c r="N48" t="str">
-        <x:v>Strength-scaled direct plus splash; weapon required; budget cap 16</x:v>
-      </x:c>
-      <x:c r="O48" t="str">
-        <x:v>Combat/TenkaichiSpecialStyles.dm</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="49">
-      <x:c r="A49" t="str">
-        <x:v>Echoing Slash</x:v>
-      </x:c>
-      <x:c r="B49" t="str">
-        <x:v>/obj/Attacks/TenkaichiSpecialStyle/ChargedProjectile/EchoingSlash</x:v>
-      </x:c>
-      <x:c r="C49" t="str">
-        <x:v>Test package</x:v>
-      </x:c>
-      <x:c r="D49" t="str">
-        <x:v>Physical</x:v>
-      </x:c>
-      <x:c r="E49" t="n">
+      <x:c r="K82" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Immediate</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L82">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M82" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Unarmed</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N82" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">15% bleed</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O82" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Combat/NexusMeleeTechniques.dm</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="83">
+      <x:c r="A83" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Texas Smash</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B83" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">/obj/Attacks/NexusMeleeTechnique/TexasSmash</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C83" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Unarmed progression</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D83" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Physical melee</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E83">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="F49" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I49" t="n">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="J49" t="n">
+      <x:c r="F83">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G83">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H83">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I83">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="J83">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="K83" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Slow impact</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L83">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M83" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Unarmed</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N83" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Extreme knockback</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O83" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Combat/NexusMeleeTechniques.dm</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="84">
+      <x:c r="A84" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Guard Break</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B84" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">/obj/Attacks/NexusMeleeTechnique/GuardBreak</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C84" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Unarmed progression</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D84" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Physical melee</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E84">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F84">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G84">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H84">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I84">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="J84">
+        <x:v>10.5</x:v>
+      </x:c>
+      <x:c r="K84" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Immediate</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L84">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M84" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Unarmed</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N84" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Breaks guard and staggers</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O84" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Combat/NexusMeleeTechniques.dm</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="85">
+      <x:c r="A85" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Wing Clip</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B85" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">/obj/Attacks/NexusMeleeTechnique/WingClip</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C85" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Unarmed progression</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D85" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Physical melee</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E85">
+        <x:v>2.75</x:v>
+      </x:c>
+      <x:c r="F85">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G85">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H85">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I85">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="J85">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K49" t="str">
-        <x:v>0.8s charge</x:v>
-      </x:c>
-      <x:c r="L49" t="n">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="M49" t="str">
-        <x:v>None</x:v>
-      </x:c>
-      <x:c r="N49" t="str">
-        <x:v>Strength-scaled cutting wave; weapon required; no explosion</x:v>
-      </x:c>
-      <x:c r="O49" t="str">
-        <x:v>Combat/TenkaichiSpecialStyles.dm</x:v>
+      <x:c r="K85" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Immediate</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L85">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M85" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Unarmed</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N85" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">High accuracy and movement stagger</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O85" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Combat/NexusMeleeTechniques.dm</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="86">
+      <x:c r="A86" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Burning Shot</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B86" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">/obj/Attacks/NexusMeleeTechnique/BurningShot</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C86" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Unarmed progression</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D86" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Physical melee</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E86">
+        <x:v>2.2</x:v>
+      </x:c>
+      <x:c r="F86">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G86">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H86">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I86">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="J86">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="K86" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Warp combo</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L86">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M86" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Unarmed</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N86" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Weighted total 5.5</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O86" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Combat/NexusMeleeTechniques.dm</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="87">
+      <x:c r="A87" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Blue Comet Special</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B87" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">/obj/Attacks/NexusMeleeTechnique/BlueCometSpecial</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C87" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Unarmed progression</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D87" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Physical melee</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E87">
+        <x:v>1.8</x:v>
+      </x:c>
+      <x:c r="F87">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G87">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H87">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I87">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="J87">
+        <x:v>17.5</x:v>
+      </x:c>
+      <x:c r="K87" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Long rush</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L87">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M87" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Unarmed</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N87" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Weighted total 6.12</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O87" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Combat/NexusMeleeTechniques.dm</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="88">
+      <x:c r="A88" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Critical Edge</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B88" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">/obj/Attacks/NexusMeleeTechnique/CriticalEdge</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C88" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Unarmed progression</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D88" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Physical melee</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E88">
+        <x:v>4.5</x:v>
+      </x:c>
+      <x:c r="F88">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G88">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H88">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I88">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J88">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="K88" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Immediate</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L88">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M88" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Unarmed</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N88" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Accurate condensed critical strike</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O88" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Combat/NexusMeleeTechniques.dm</x:t>
+        </x:is>
       </x:c>
     </x:row>
   </x:sheetData>
